--- a/2026-scrimmage/public/games/Canada_Korea_G2_Scrimmage_2026.xlsx
+++ b/2026-scrimmage/public/games/Canada_Korea_G2_Scrimmage_2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/eb80e08bdabfb8fb/Documents/NAC SPORT DATA/Categories/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ahmui\Claude Projects\goalball-dashboard\2026-scrimmage\public\games\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_08BC1311ADC42E926F7E5614B9EB3C0309F2072A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7FFE83D7-3A5C-4D94-BA1D-26995E1F9DFC}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3B8709F-2180-4266-BBF0-AA39AA19ADE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="11700" windowHeight="14730" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3130" uniqueCount="1454">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3690" uniqueCount="1456">
   <si>
     <t>N#</t>
   </si>
@@ -4382,6 +4382,12 @@
   </si>
   <si>
     <t>54:05</t>
+  </si>
+  <si>
+    <t>Malmo</t>
+  </si>
+  <si>
+    <t>South Korea</t>
   </si>
 </sst>
 </file>
@@ -6826,8 +6832,8 @@
       </c>
     </row>
     <row r="2" spans="1:700" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="s">
+        <v>1455</v>
       </c>
       <c r="B2" t="s">
         <v>700</v>
@@ -6841,10 +6847,13 @@
       <c r="E2" t="s">
         <v>701</v>
       </c>
+      <c r="F2" t="s">
+        <v>1454</v>
+      </c>
     </row>
     <row r="3" spans="1:700" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>1</v>
+      <c r="A3" t="s">
+        <v>1455</v>
       </c>
       <c r="B3" t="s">
         <v>702</v>
@@ -6858,10 +6867,13 @@
       <c r="E3" t="s">
         <v>701</v>
       </c>
+      <c r="F3" t="s">
+        <v>1454</v>
+      </c>
     </row>
     <row r="4" spans="1:700" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>1</v>
+      <c r="A4" t="s">
+        <v>1455</v>
       </c>
       <c r="B4" t="s">
         <v>703</v>
@@ -6875,6 +6887,9 @@
       <c r="E4" t="s">
         <v>706</v>
       </c>
+      <c r="F4" t="s">
+        <v>1454</v>
+      </c>
       <c r="G4" t="s">
         <v>707</v>
       </c>
@@ -6892,8 +6907,8 @@
       </c>
     </row>
     <row r="5" spans="1:700" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>1</v>
+      <c r="A5" t="s">
+        <v>1455</v>
       </c>
       <c r="B5" t="s">
         <v>712</v>
@@ -6907,6 +6922,9 @@
       <c r="E5" t="s">
         <v>715</v>
       </c>
+      <c r="F5" t="s">
+        <v>1454</v>
+      </c>
       <c r="G5" t="s">
         <v>716</v>
       </c>
@@ -6924,8 +6942,8 @@
       </c>
     </row>
     <row r="6" spans="1:700" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>2</v>
+      <c r="A6" t="s">
+        <v>1455</v>
       </c>
       <c r="B6" t="s">
         <v>703</v>
@@ -6939,6 +6957,9 @@
       <c r="E6" t="s">
         <v>722</v>
       </c>
+      <c r="F6" t="s">
+        <v>1454</v>
+      </c>
       <c r="G6" t="s">
         <v>723</v>
       </c>
@@ -6956,8 +6977,8 @@
       </c>
     </row>
     <row r="7" spans="1:700" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>2</v>
+      <c r="A7" t="s">
+        <v>1455</v>
       </c>
       <c r="B7" t="s">
         <v>712</v>
@@ -6971,6 +6992,9 @@
       <c r="E7" t="s">
         <v>728</v>
       </c>
+      <c r="F7" t="s">
+        <v>1454</v>
+      </c>
       <c r="G7" t="s">
         <v>716</v>
       </c>
@@ -6988,8 +7012,8 @@
       </c>
     </row>
     <row r="8" spans="1:700" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>3</v>
+      <c r="A8" t="s">
+        <v>1455</v>
       </c>
       <c r="B8" t="s">
         <v>703</v>
@@ -7003,6 +7027,9 @@
       <c r="E8" t="s">
         <v>732</v>
       </c>
+      <c r="F8" t="s">
+        <v>1454</v>
+      </c>
       <c r="G8" t="s">
         <v>707</v>
       </c>
@@ -7020,8 +7047,8 @@
       </c>
     </row>
     <row r="9" spans="1:700" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>3</v>
+      <c r="A9" t="s">
+        <v>1455</v>
       </c>
       <c r="B9" t="s">
         <v>712</v>
@@ -7035,6 +7062,9 @@
       <c r="E9" t="s">
         <v>736</v>
       </c>
+      <c r="F9" t="s">
+        <v>1454</v>
+      </c>
       <c r="G9" t="s">
         <v>734</v>
       </c>
@@ -7052,8 +7082,8 @@
       </c>
     </row>
     <row r="10" spans="1:700" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>4</v>
+      <c r="A10" t="s">
+        <v>1455</v>
       </c>
       <c r="B10" t="s">
         <v>703</v>
@@ -7067,6 +7097,9 @@
       <c r="E10" t="s">
         <v>739</v>
       </c>
+      <c r="F10" t="s">
+        <v>1454</v>
+      </c>
       <c r="G10" t="s">
         <v>707</v>
       </c>
@@ -7081,8 +7114,8 @@
       </c>
     </row>
     <row r="11" spans="1:700" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>4</v>
+      <c r="A11" t="s">
+        <v>1455</v>
       </c>
       <c r="B11" t="s">
         <v>712</v>
@@ -7096,6 +7129,9 @@
       <c r="E11" t="s">
         <v>744</v>
       </c>
+      <c r="F11" t="s">
+        <v>1454</v>
+      </c>
       <c r="G11" t="s">
         <v>716</v>
       </c>
@@ -7113,8 +7149,8 @@
       </c>
     </row>
     <row r="12" spans="1:700" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>5</v>
+      <c r="A12" t="s">
+        <v>1455</v>
       </c>
       <c r="B12" t="s">
         <v>703</v>
@@ -7128,6 +7164,9 @@
       <c r="E12" t="s">
         <v>747</v>
       </c>
+      <c r="F12" t="s">
+        <v>1454</v>
+      </c>
       <c r="G12" t="s">
         <v>707</v>
       </c>
@@ -7145,8 +7184,8 @@
       </c>
     </row>
     <row r="13" spans="1:700" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>5</v>
+      <c r="A13" t="s">
+        <v>1455</v>
       </c>
       <c r="B13" t="s">
         <v>712</v>
@@ -7160,6 +7199,9 @@
       <c r="E13" t="s">
         <v>751</v>
       </c>
+      <c r="F13" t="s">
+        <v>1454</v>
+      </c>
       <c r="G13" t="s">
         <v>734</v>
       </c>
@@ -7177,8 +7219,8 @@
       </c>
     </row>
     <row r="14" spans="1:700" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>6</v>
+      <c r="A14" t="s">
+        <v>1455</v>
       </c>
       <c r="B14" t="s">
         <v>703</v>
@@ -7192,6 +7234,9 @@
       <c r="E14" t="s">
         <v>753</v>
       </c>
+      <c r="F14" t="s">
+        <v>1454</v>
+      </c>
       <c r="G14" t="s">
         <v>723</v>
       </c>
@@ -7206,8 +7251,8 @@
       </c>
     </row>
     <row r="15" spans="1:700" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>6</v>
+      <c r="A15" t="s">
+        <v>1455</v>
       </c>
       <c r="B15" t="s">
         <v>712</v>
@@ -7221,6 +7266,9 @@
       <c r="E15" t="s">
         <v>757</v>
       </c>
+      <c r="F15" t="s">
+        <v>1454</v>
+      </c>
       <c r="G15" t="s">
         <v>734</v>
       </c>
@@ -7238,8 +7286,8 @@
       </c>
     </row>
     <row r="16" spans="1:700" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>7</v>
+      <c r="A16" t="s">
+        <v>1455</v>
       </c>
       <c r="B16" t="s">
         <v>703</v>
@@ -7253,6 +7301,9 @@
       <c r="E16" t="s">
         <v>760</v>
       </c>
+      <c r="F16" t="s">
+        <v>1454</v>
+      </c>
       <c r="G16" t="s">
         <v>719</v>
       </c>
@@ -7270,8 +7321,8 @@
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>7</v>
+      <c r="A17" t="s">
+        <v>1455</v>
       </c>
       <c r="B17" t="s">
         <v>712</v>
@@ -7285,6 +7336,9 @@
       <c r="E17" t="s">
         <v>762</v>
       </c>
+      <c r="F17" t="s">
+        <v>1454</v>
+      </c>
       <c r="G17" t="s">
         <v>734</v>
       </c>
@@ -7302,8 +7356,8 @@
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>8</v>
+      <c r="A18" t="s">
+        <v>1455</v>
       </c>
       <c r="B18" t="s">
         <v>703</v>
@@ -7317,6 +7371,9 @@
       <c r="E18" t="s">
         <v>765</v>
       </c>
+      <c r="F18" t="s">
+        <v>1454</v>
+      </c>
       <c r="G18" t="s">
         <v>723</v>
       </c>
@@ -7334,8 +7391,8 @@
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>8</v>
+      <c r="A19" t="s">
+        <v>1455</v>
       </c>
       <c r="B19" t="s">
         <v>712</v>
@@ -7349,6 +7406,9 @@
       <c r="E19" t="s">
         <v>768</v>
       </c>
+      <c r="F19" t="s">
+        <v>1454</v>
+      </c>
       <c r="G19" t="s">
         <v>734</v>
       </c>
@@ -7366,8 +7426,8 @@
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>9</v>
+      <c r="A20" t="s">
+        <v>1455</v>
       </c>
       <c r="B20" t="s">
         <v>703</v>
@@ -7381,6 +7441,9 @@
       <c r="E20" t="s">
         <v>769</v>
       </c>
+      <c r="F20" t="s">
+        <v>1454</v>
+      </c>
       <c r="G20" t="s">
         <v>707</v>
       </c>
@@ -7398,8 +7461,8 @@
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>9</v>
+      <c r="A21" t="s">
+        <v>1455</v>
       </c>
       <c r="B21" t="s">
         <v>712</v>
@@ -7413,6 +7476,9 @@
       <c r="E21" t="s">
         <v>773</v>
       </c>
+      <c r="F21" t="s">
+        <v>1454</v>
+      </c>
       <c r="G21" t="s">
         <v>716</v>
       </c>
@@ -7433,8 +7499,8 @@
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>10</v>
+      <c r="A22" t="s">
+        <v>1455</v>
       </c>
       <c r="B22" t="s">
         <v>712</v>
@@ -7448,6 +7514,9 @@
       <c r="E22" t="s">
         <v>778</v>
       </c>
+      <c r="F22" t="s">
+        <v>1454</v>
+      </c>
       <c r="G22" t="s">
         <v>734</v>
       </c>
@@ -7465,8 +7534,8 @@
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>10</v>
+      <c r="A23" t="s">
+        <v>1455</v>
       </c>
       <c r="B23" t="s">
         <v>703</v>
@@ -7480,6 +7549,9 @@
       <c r="E23" t="s">
         <v>780</v>
       </c>
+      <c r="F23" t="s">
+        <v>1454</v>
+      </c>
       <c r="G23" t="s">
         <v>707</v>
       </c>
@@ -7497,8 +7569,8 @@
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>11</v>
+      <c r="A24" t="s">
+        <v>1455</v>
       </c>
       <c r="B24" t="s">
         <v>712</v>
@@ -7512,6 +7584,9 @@
       <c r="E24" t="s">
         <v>783</v>
       </c>
+      <c r="F24" t="s">
+        <v>1454</v>
+      </c>
       <c r="G24" t="s">
         <v>716</v>
       </c>
@@ -7529,8 +7604,8 @@
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>11</v>
+      <c r="A25" t="s">
+        <v>1455</v>
       </c>
       <c r="B25" t="s">
         <v>703</v>
@@ -7544,6 +7619,9 @@
       <c r="E25" t="s">
         <v>786</v>
       </c>
+      <c r="F25" t="s">
+        <v>1454</v>
+      </c>
       <c r="G25" t="s">
         <v>707</v>
       </c>
@@ -7561,8 +7639,8 @@
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26">
-        <v>12</v>
+      <c r="A26" t="s">
+        <v>1455</v>
       </c>
       <c r="B26" t="s">
         <v>712</v>
@@ -7576,6 +7654,9 @@
       <c r="E26" t="s">
         <v>788</v>
       </c>
+      <c r="F26" t="s">
+        <v>1454</v>
+      </c>
       <c r="G26" t="s">
         <v>734</v>
       </c>
@@ -7593,8 +7674,8 @@
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27">
-        <v>12</v>
+      <c r="A27" t="s">
+        <v>1455</v>
       </c>
       <c r="B27" t="s">
         <v>703</v>
@@ -7608,6 +7689,9 @@
       <c r="E27" t="s">
         <v>791</v>
       </c>
+      <c r="F27" t="s">
+        <v>1454</v>
+      </c>
       <c r="G27" t="s">
         <v>707</v>
       </c>
@@ -7625,8 +7709,8 @@
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <v>13</v>
+      <c r="A28" t="s">
+        <v>1455</v>
       </c>
       <c r="B28" t="s">
         <v>712</v>
@@ -7640,6 +7724,9 @@
       <c r="E28" t="s">
         <v>793</v>
       </c>
+      <c r="F28" t="s">
+        <v>1454</v>
+      </c>
       <c r="G28" t="s">
         <v>716</v>
       </c>
@@ -7657,8 +7744,8 @@
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <v>13</v>
+      <c r="A29" t="s">
+        <v>1455</v>
       </c>
       <c r="B29" t="s">
         <v>703</v>
@@ -7672,6 +7759,9 @@
       <c r="E29" t="s">
         <v>796</v>
       </c>
+      <c r="F29" t="s">
+        <v>1454</v>
+      </c>
       <c r="G29" t="s">
         <v>723</v>
       </c>
@@ -7689,8 +7779,8 @@
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <v>14</v>
+      <c r="A30" t="s">
+        <v>1455</v>
       </c>
       <c r="B30" t="s">
         <v>712</v>
@@ -7704,6 +7794,9 @@
       <c r="E30" t="s">
         <v>799</v>
       </c>
+      <c r="F30" t="s">
+        <v>1454</v>
+      </c>
       <c r="G30" t="s">
         <v>716</v>
       </c>
@@ -7721,8 +7814,8 @@
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <v>14</v>
+      <c r="A31" t="s">
+        <v>1455</v>
       </c>
       <c r="B31" t="s">
         <v>703</v>
@@ -7736,6 +7829,9 @@
       <c r="E31" t="s">
         <v>802</v>
       </c>
+      <c r="F31" t="s">
+        <v>1454</v>
+      </c>
       <c r="G31" t="s">
         <v>723</v>
       </c>
@@ -7753,8 +7849,8 @@
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <v>15</v>
+      <c r="A32" t="s">
+        <v>1455</v>
       </c>
       <c r="B32" t="s">
         <v>712</v>
@@ -7768,6 +7864,9 @@
       <c r="E32" t="s">
         <v>805</v>
       </c>
+      <c r="F32" t="s">
+        <v>1454</v>
+      </c>
       <c r="G32" t="s">
         <v>734</v>
       </c>
@@ -7785,8 +7884,8 @@
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A33">
-        <v>15</v>
+      <c r="A33" t="s">
+        <v>1455</v>
       </c>
       <c r="B33" t="s">
         <v>703</v>
@@ -7800,6 +7899,9 @@
       <c r="E33" t="s">
         <v>808</v>
       </c>
+      <c r="F33" t="s">
+        <v>1454</v>
+      </c>
       <c r="G33" t="s">
         <v>707</v>
       </c>
@@ -7817,8 +7919,8 @@
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A34">
-        <v>16</v>
+      <c r="A34" t="s">
+        <v>1455</v>
       </c>
       <c r="B34" t="s">
         <v>712</v>
@@ -7832,6 +7934,9 @@
       <c r="E34" t="s">
         <v>810</v>
       </c>
+      <c r="F34" t="s">
+        <v>1454</v>
+      </c>
       <c r="G34" t="s">
         <v>734</v>
       </c>
@@ -7849,8 +7954,8 @@
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A35">
-        <v>16</v>
+      <c r="A35" t="s">
+        <v>1455</v>
       </c>
       <c r="B35" t="s">
         <v>703</v>
@@ -7864,6 +7969,9 @@
       <c r="E35" t="s">
         <v>813</v>
       </c>
+      <c r="F35" t="s">
+        <v>1454</v>
+      </c>
       <c r="G35" t="s">
         <v>707</v>
       </c>
@@ -7881,8 +7989,8 @@
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A36">
-        <v>17</v>
+      <c r="A36" t="s">
+        <v>1455</v>
       </c>
       <c r="B36" t="s">
         <v>712</v>
@@ -7896,6 +8004,9 @@
       <c r="E36" t="s">
         <v>816</v>
       </c>
+      <c r="F36" t="s">
+        <v>1454</v>
+      </c>
       <c r="G36" t="s">
         <v>734</v>
       </c>
@@ -7913,8 +8024,8 @@
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A37">
-        <v>17</v>
+      <c r="A37" t="s">
+        <v>1455</v>
       </c>
       <c r="B37" t="s">
         <v>703</v>
@@ -7928,6 +8039,9 @@
       <c r="E37" t="s">
         <v>819</v>
       </c>
+      <c r="F37" t="s">
+        <v>1454</v>
+      </c>
       <c r="G37" t="s">
         <v>723</v>
       </c>
@@ -7945,8 +8059,8 @@
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A38">
-        <v>18</v>
+      <c r="A38" t="s">
+        <v>1455</v>
       </c>
       <c r="B38" t="s">
         <v>712</v>
@@ -7960,6 +8074,9 @@
       <c r="E38" t="s">
         <v>821</v>
       </c>
+      <c r="F38" t="s">
+        <v>1454</v>
+      </c>
       <c r="G38" t="s">
         <v>716</v>
       </c>
@@ -7980,8 +8097,8 @@
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A39">
-        <v>18</v>
+      <c r="A39" t="s">
+        <v>1455</v>
       </c>
       <c r="B39" t="s">
         <v>703</v>
@@ -7995,10 +8112,13 @@
       <c r="E39" t="s">
         <v>824</v>
       </c>
+      <c r="F39" t="s">
+        <v>1454</v>
+      </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A40">
-        <v>19</v>
+      <c r="A40" t="s">
+        <v>1455</v>
       </c>
       <c r="B40" t="s">
         <v>712</v>
@@ -8012,6 +8132,9 @@
       <c r="E40" t="s">
         <v>827</v>
       </c>
+      <c r="F40" t="s">
+        <v>1454</v>
+      </c>
       <c r="G40" t="s">
         <v>716</v>
       </c>
@@ -8029,8 +8152,8 @@
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A41">
-        <v>19</v>
+      <c r="A41" t="s">
+        <v>1455</v>
       </c>
       <c r="B41" t="s">
         <v>703</v>
@@ -8044,6 +8167,9 @@
       <c r="E41" t="s">
         <v>830</v>
       </c>
+      <c r="F41" t="s">
+        <v>1454</v>
+      </c>
       <c r="G41" t="s">
         <v>723</v>
       </c>
@@ -8061,8 +8187,8 @@
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A42">
-        <v>20</v>
+      <c r="A42" t="s">
+        <v>1455</v>
       </c>
       <c r="B42" t="s">
         <v>712</v>
@@ -8076,6 +8202,9 @@
       <c r="E42" t="s">
         <v>832</v>
       </c>
+      <c r="F42" t="s">
+        <v>1454</v>
+      </c>
       <c r="G42" t="s">
         <v>734</v>
       </c>
@@ -8093,8 +8222,8 @@
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A43">
-        <v>20</v>
+      <c r="A43" t="s">
+        <v>1455</v>
       </c>
       <c r="B43" t="s">
         <v>703</v>
@@ -8108,6 +8237,9 @@
       <c r="E43" t="s">
         <v>835</v>
       </c>
+      <c r="F43" t="s">
+        <v>1454</v>
+      </c>
       <c r="G43" t="s">
         <v>707</v>
       </c>
@@ -8125,8 +8257,8 @@
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A44">
-        <v>21</v>
+      <c r="A44" t="s">
+        <v>1455</v>
       </c>
       <c r="B44" t="s">
         <v>712</v>
@@ -8140,6 +8272,9 @@
       <c r="E44" t="s">
         <v>838</v>
       </c>
+      <c r="F44" t="s">
+        <v>1454</v>
+      </c>
       <c r="G44" t="s">
         <v>716</v>
       </c>
@@ -8157,8 +8292,8 @@
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A45">
-        <v>21</v>
+      <c r="A45" t="s">
+        <v>1455</v>
       </c>
       <c r="B45" t="s">
         <v>703</v>
@@ -8172,6 +8307,9 @@
       <c r="E45" t="s">
         <v>841</v>
       </c>
+      <c r="F45" t="s">
+        <v>1454</v>
+      </c>
       <c r="G45" t="s">
         <v>723</v>
       </c>
@@ -8189,8 +8327,8 @@
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A46">
-        <v>22</v>
+      <c r="A46" t="s">
+        <v>1455</v>
       </c>
       <c r="B46" t="s">
         <v>712</v>
@@ -8204,6 +8342,9 @@
       <c r="E46" t="s">
         <v>842</v>
       </c>
+      <c r="F46" t="s">
+        <v>1454</v>
+      </c>
       <c r="G46" t="s">
         <v>734</v>
       </c>
@@ -8221,8 +8362,8 @@
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A47">
-        <v>22</v>
+      <c r="A47" t="s">
+        <v>1455</v>
       </c>
       <c r="B47" t="s">
         <v>703</v>
@@ -8236,6 +8377,9 @@
       <c r="E47" t="s">
         <v>844</v>
       </c>
+      <c r="F47" t="s">
+        <v>1454</v>
+      </c>
       <c r="G47" t="s">
         <v>723</v>
       </c>
@@ -8253,8 +8397,8 @@
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A48">
-        <v>23</v>
+      <c r="A48" t="s">
+        <v>1455</v>
       </c>
       <c r="B48" t="s">
         <v>712</v>
@@ -8268,6 +8412,9 @@
       <c r="E48" t="s">
         <v>846</v>
       </c>
+      <c r="F48" t="s">
+        <v>1454</v>
+      </c>
       <c r="G48" t="s">
         <v>716</v>
       </c>
@@ -8285,8 +8432,8 @@
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A49">
-        <v>23</v>
+      <c r="A49" t="s">
+        <v>1455</v>
       </c>
       <c r="B49" t="s">
         <v>703</v>
@@ -8300,6 +8447,9 @@
       <c r="E49" t="s">
         <v>849</v>
       </c>
+      <c r="F49" t="s">
+        <v>1454</v>
+      </c>
       <c r="G49" t="s">
         <v>707</v>
       </c>
@@ -8317,8 +8467,8 @@
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A50">
-        <v>24</v>
+      <c r="A50" t="s">
+        <v>1455</v>
       </c>
       <c r="B50" t="s">
         <v>712</v>
@@ -8332,6 +8482,9 @@
       <c r="E50" t="s">
         <v>852</v>
       </c>
+      <c r="F50" t="s">
+        <v>1454</v>
+      </c>
       <c r="G50" t="s">
         <v>734</v>
       </c>
@@ -8349,8 +8502,8 @@
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A51">
-        <v>24</v>
+      <c r="A51" t="s">
+        <v>1455</v>
       </c>
       <c r="B51" t="s">
         <v>703</v>
@@ -8364,6 +8517,9 @@
       <c r="E51" t="s">
         <v>855</v>
       </c>
+      <c r="F51" t="s">
+        <v>1454</v>
+      </c>
       <c r="G51" t="s">
         <v>719</v>
       </c>
@@ -8381,8 +8537,8 @@
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A52">
-        <v>25</v>
+      <c r="A52" t="s">
+        <v>1455</v>
       </c>
       <c r="B52" t="s">
         <v>712</v>
@@ -8396,6 +8552,9 @@
       <c r="E52" t="s">
         <v>858</v>
       </c>
+      <c r="F52" t="s">
+        <v>1454</v>
+      </c>
       <c r="G52" t="s">
         <v>716</v>
       </c>
@@ -8413,8 +8572,8 @@
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A53">
-        <v>25</v>
+      <c r="A53" t="s">
+        <v>1455</v>
       </c>
       <c r="B53" t="s">
         <v>703</v>
@@ -8428,6 +8587,9 @@
       <c r="E53" t="s">
         <v>861</v>
       </c>
+      <c r="F53" t="s">
+        <v>1454</v>
+      </c>
       <c r="G53" t="s">
         <v>723</v>
       </c>
@@ -8445,8 +8607,8 @@
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A54">
-        <v>26</v>
+      <c r="A54" t="s">
+        <v>1455</v>
       </c>
       <c r="B54" t="s">
         <v>712</v>
@@ -8460,6 +8622,9 @@
       <c r="E54" t="s">
         <v>865</v>
       </c>
+      <c r="F54" t="s">
+        <v>1454</v>
+      </c>
       <c r="G54" t="s">
         <v>734</v>
       </c>
@@ -8477,8 +8642,8 @@
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A55">
-        <v>26</v>
+      <c r="A55" t="s">
+        <v>1455</v>
       </c>
       <c r="B55" t="s">
         <v>703</v>
@@ -8492,6 +8657,9 @@
       <c r="E55" t="s">
         <v>868</v>
       </c>
+      <c r="F55" t="s">
+        <v>1454</v>
+      </c>
       <c r="G55" t="s">
         <v>719</v>
       </c>
@@ -8509,8 +8677,8 @@
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A56">
-        <v>27</v>
+      <c r="A56" t="s">
+        <v>1455</v>
       </c>
       <c r="B56" t="s">
         <v>712</v>
@@ -8524,6 +8692,9 @@
       <c r="E56" t="s">
         <v>870</v>
       </c>
+      <c r="F56" t="s">
+        <v>1454</v>
+      </c>
       <c r="G56" t="s">
         <v>716</v>
       </c>
@@ -8541,8 +8712,8 @@
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A57">
-        <v>27</v>
+      <c r="A57" t="s">
+        <v>1455</v>
       </c>
       <c r="B57" t="s">
         <v>703</v>
@@ -8556,6 +8727,9 @@
       <c r="E57" t="s">
         <v>873</v>
       </c>
+      <c r="F57" t="s">
+        <v>1454</v>
+      </c>
       <c r="G57" t="s">
         <v>719</v>
       </c>
@@ -8573,8 +8747,8 @@
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A58">
-        <v>28</v>
+      <c r="A58" t="s">
+        <v>1455</v>
       </c>
       <c r="B58" t="s">
         <v>712</v>
@@ -8588,6 +8762,9 @@
       <c r="E58" t="s">
         <v>874</v>
       </c>
+      <c r="F58" t="s">
+        <v>1454</v>
+      </c>
       <c r="G58" t="s">
         <v>734</v>
       </c>
@@ -8605,8 +8782,8 @@
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A59">
-        <v>28</v>
+      <c r="A59" t="s">
+        <v>1455</v>
       </c>
       <c r="B59" t="s">
         <v>703</v>
@@ -8620,6 +8797,9 @@
       <c r="E59" t="s">
         <v>876</v>
       </c>
+      <c r="F59" t="s">
+        <v>1454</v>
+      </c>
       <c r="G59" t="s">
         <v>723</v>
       </c>
@@ -8637,8 +8817,8 @@
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A60">
-        <v>29</v>
+      <c r="A60" t="s">
+        <v>1455</v>
       </c>
       <c r="B60" t="s">
         <v>712</v>
@@ -8652,6 +8832,9 @@
       <c r="E60" t="s">
         <v>879</v>
       </c>
+      <c r="F60" t="s">
+        <v>1454</v>
+      </c>
       <c r="G60" t="s">
         <v>734</v>
       </c>
@@ -8669,8 +8852,8 @@
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A61">
-        <v>29</v>
+      <c r="A61" t="s">
+        <v>1455</v>
       </c>
       <c r="B61" t="s">
         <v>703</v>
@@ -8684,6 +8867,9 @@
       <c r="E61" t="s">
         <v>882</v>
       </c>
+      <c r="F61" t="s">
+        <v>1454</v>
+      </c>
       <c r="G61" t="s">
         <v>723</v>
       </c>
@@ -8701,8 +8887,8 @@
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A62">
-        <v>30</v>
+      <c r="A62" t="s">
+        <v>1455</v>
       </c>
       <c r="B62" t="s">
         <v>712</v>
@@ -8716,6 +8902,9 @@
       <c r="E62" t="s">
         <v>885</v>
       </c>
+      <c r="F62" t="s">
+        <v>1454</v>
+      </c>
       <c r="G62" t="s">
         <v>716</v>
       </c>
@@ -8733,8 +8922,8 @@
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A63">
-        <v>30</v>
+      <c r="A63" t="s">
+        <v>1455</v>
       </c>
       <c r="B63" t="s">
         <v>703</v>
@@ -8748,6 +8937,9 @@
       <c r="E63" t="s">
         <v>887</v>
       </c>
+      <c r="F63" t="s">
+        <v>1454</v>
+      </c>
       <c r="G63" t="s">
         <v>723</v>
       </c>
@@ -8765,8 +8957,8 @@
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A64">
-        <v>31</v>
+      <c r="A64" t="s">
+        <v>1455</v>
       </c>
       <c r="B64" t="s">
         <v>712</v>
@@ -8780,6 +8972,9 @@
       <c r="E64" t="s">
         <v>890</v>
       </c>
+      <c r="F64" t="s">
+        <v>1454</v>
+      </c>
       <c r="G64" t="s">
         <v>734</v>
       </c>
@@ -8797,8 +8992,8 @@
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A65">
-        <v>31</v>
+      <c r="A65" t="s">
+        <v>1455</v>
       </c>
       <c r="B65" t="s">
         <v>703</v>
@@ -8812,6 +9007,9 @@
       <c r="E65" t="s">
         <v>893</v>
       </c>
+      <c r="F65" t="s">
+        <v>1454</v>
+      </c>
       <c r="G65" t="s">
         <v>719</v>
       </c>
@@ -8829,8 +9027,8 @@
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A66">
-        <v>32</v>
+      <c r="A66" t="s">
+        <v>1455</v>
       </c>
       <c r="B66" t="s">
         <v>712</v>
@@ -8844,6 +9042,9 @@
       <c r="E66" t="s">
         <v>896</v>
       </c>
+      <c r="F66" t="s">
+        <v>1454</v>
+      </c>
       <c r="G66" t="s">
         <v>716</v>
       </c>
@@ -8861,8 +9062,8 @@
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A67">
-        <v>32</v>
+      <c r="A67" t="s">
+        <v>1455</v>
       </c>
       <c r="B67" t="s">
         <v>703</v>
@@ -8876,6 +9077,9 @@
       <c r="E67" t="s">
         <v>898</v>
       </c>
+      <c r="F67" t="s">
+        <v>1454</v>
+      </c>
       <c r="G67" t="s">
         <v>719</v>
       </c>
@@ -8893,8 +9097,8 @@
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A68">
-        <v>33</v>
+      <c r="A68" t="s">
+        <v>1455</v>
       </c>
       <c r="B68" t="s">
         <v>712</v>
@@ -8908,6 +9112,9 @@
       <c r="E68" t="s">
         <v>901</v>
       </c>
+      <c r="F68" t="s">
+        <v>1454</v>
+      </c>
       <c r="G68" t="s">
         <v>734</v>
       </c>
@@ -8925,8 +9132,8 @@
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A69">
-        <v>33</v>
+      <c r="A69" t="s">
+        <v>1455</v>
       </c>
       <c r="B69" t="s">
         <v>703</v>
@@ -8940,6 +9147,9 @@
       <c r="E69" t="s">
         <v>904</v>
       </c>
+      <c r="F69" t="s">
+        <v>1454</v>
+      </c>
       <c r="G69" t="s">
         <v>719</v>
       </c>
@@ -8957,8 +9167,8 @@
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A70">
-        <v>34</v>
+      <c r="A70" t="s">
+        <v>1455</v>
       </c>
       <c r="B70" t="s">
         <v>712</v>
@@ -8972,6 +9182,9 @@
       <c r="E70" t="s">
         <v>907</v>
       </c>
+      <c r="F70" t="s">
+        <v>1454</v>
+      </c>
       <c r="G70" t="s">
         <v>716</v>
       </c>
@@ -8989,8 +9202,8 @@
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A71">
-        <v>34</v>
+      <c r="A71" t="s">
+        <v>1455</v>
       </c>
       <c r="B71" t="s">
         <v>703</v>
@@ -9004,6 +9217,9 @@
       <c r="E71" t="s">
         <v>909</v>
       </c>
+      <c r="F71" t="s">
+        <v>1454</v>
+      </c>
       <c r="G71" t="s">
         <v>723</v>
       </c>
@@ -9021,8 +9237,8 @@
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A72">
-        <v>35</v>
+      <c r="A72" t="s">
+        <v>1455</v>
       </c>
       <c r="B72" t="s">
         <v>712</v>
@@ -9036,6 +9252,9 @@
       <c r="E72" t="s">
         <v>912</v>
       </c>
+      <c r="F72" t="s">
+        <v>1454</v>
+      </c>
       <c r="G72" t="s">
         <v>716</v>
       </c>
@@ -9053,8 +9272,8 @@
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A73">
-        <v>35</v>
+      <c r="A73" t="s">
+        <v>1455</v>
       </c>
       <c r="B73" t="s">
         <v>703</v>
@@ -9068,6 +9287,9 @@
       <c r="E73" t="s">
         <v>914</v>
       </c>
+      <c r="F73" t="s">
+        <v>1454</v>
+      </c>
       <c r="G73" t="s">
         <v>707</v>
       </c>
@@ -9085,8 +9307,8 @@
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A74">
-        <v>36</v>
+      <c r="A74" t="s">
+        <v>1455</v>
       </c>
       <c r="B74" t="s">
         <v>712</v>
@@ -9100,6 +9322,9 @@
       <c r="E74" t="s">
         <v>917</v>
       </c>
+      <c r="F74" t="s">
+        <v>1454</v>
+      </c>
       <c r="G74" t="s">
         <v>716</v>
       </c>
@@ -9117,8 +9342,8 @@
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A75">
-        <v>36</v>
+      <c r="A75" t="s">
+        <v>1455</v>
       </c>
       <c r="B75" t="s">
         <v>703</v>
@@ -9132,6 +9357,9 @@
       <c r="E75" t="s">
         <v>919</v>
       </c>
+      <c r="F75" t="s">
+        <v>1454</v>
+      </c>
       <c r="G75" t="s">
         <v>723</v>
       </c>
@@ -9149,8 +9377,8 @@
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A76">
-        <v>37</v>
+      <c r="A76" t="s">
+        <v>1455</v>
       </c>
       <c r="B76" t="s">
         <v>712</v>
@@ -9164,6 +9392,9 @@
       <c r="E76" t="s">
         <v>922</v>
       </c>
+      <c r="F76" t="s">
+        <v>1454</v>
+      </c>
       <c r="G76" t="s">
         <v>734</v>
       </c>
@@ -9181,8 +9412,8 @@
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A77">
-        <v>37</v>
+      <c r="A77" t="s">
+        <v>1455</v>
       </c>
       <c r="B77" t="s">
         <v>703</v>
@@ -9196,6 +9427,9 @@
       <c r="E77" t="s">
         <v>924</v>
       </c>
+      <c r="F77" t="s">
+        <v>1454</v>
+      </c>
       <c r="G77" t="s">
         <v>723</v>
       </c>
@@ -9213,8 +9447,8 @@
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A78">
-        <v>38</v>
+      <c r="A78" t="s">
+        <v>1455</v>
       </c>
       <c r="B78" t="s">
         <v>712</v>
@@ -9228,6 +9462,9 @@
       <c r="E78" t="s">
         <v>927</v>
       </c>
+      <c r="F78" t="s">
+        <v>1454</v>
+      </c>
       <c r="G78" t="s">
         <v>716</v>
       </c>
@@ -9245,8 +9482,8 @@
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A79">
-        <v>38</v>
+      <c r="A79" t="s">
+        <v>1455</v>
       </c>
       <c r="B79" t="s">
         <v>703</v>
@@ -9260,6 +9497,9 @@
       <c r="E79" t="s">
         <v>930</v>
       </c>
+      <c r="F79" t="s">
+        <v>1454</v>
+      </c>
       <c r="G79" t="s">
         <v>723</v>
       </c>
@@ -9277,8 +9517,8 @@
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A80">
-        <v>39</v>
+      <c r="A80" t="s">
+        <v>1455</v>
       </c>
       <c r="B80" t="s">
         <v>712</v>
@@ -9292,10 +9532,13 @@
       <c r="E80" t="s">
         <v>933</v>
       </c>
+      <c r="F80" t="s">
+        <v>1454</v>
+      </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A81">
-        <v>39</v>
+      <c r="A81" t="s">
+        <v>1455</v>
       </c>
       <c r="B81" t="s">
         <v>703</v>
@@ -9309,6 +9552,9 @@
       <c r="E81" t="s">
         <v>936</v>
       </c>
+      <c r="F81" t="s">
+        <v>1454</v>
+      </c>
       <c r="G81" t="s">
         <v>719</v>
       </c>
@@ -9326,8 +9572,8 @@
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A82">
-        <v>40</v>
+      <c r="A82" t="s">
+        <v>1455</v>
       </c>
       <c r="B82" t="s">
         <v>712</v>
@@ -9341,6 +9587,9 @@
       <c r="E82" t="s">
         <v>939</v>
       </c>
+      <c r="F82" t="s">
+        <v>1454</v>
+      </c>
       <c r="G82" t="s">
         <v>716</v>
       </c>
@@ -9358,8 +9607,8 @@
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A83">
-        <v>40</v>
+      <c r="A83" t="s">
+        <v>1455</v>
       </c>
       <c r="B83" t="s">
         <v>703</v>
@@ -9373,6 +9622,9 @@
       <c r="E83" t="s">
         <v>942</v>
       </c>
+      <c r="F83" t="s">
+        <v>1454</v>
+      </c>
       <c r="G83" t="s">
         <v>723</v>
       </c>
@@ -9390,8 +9642,8 @@
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A84">
-        <v>41</v>
+      <c r="A84" t="s">
+        <v>1455</v>
       </c>
       <c r="B84" t="s">
         <v>712</v>
@@ -9405,6 +9657,9 @@
       <c r="E84" t="s">
         <v>945</v>
       </c>
+      <c r="F84" t="s">
+        <v>1454</v>
+      </c>
       <c r="G84" t="s">
         <v>734</v>
       </c>
@@ -9422,8 +9677,8 @@
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A85">
-        <v>41</v>
+      <c r="A85" t="s">
+        <v>1455</v>
       </c>
       <c r="B85" t="s">
         <v>703</v>
@@ -9437,6 +9692,9 @@
       <c r="E85" t="s">
         <v>948</v>
       </c>
+      <c r="F85" t="s">
+        <v>1454</v>
+      </c>
       <c r="G85" t="s">
         <v>719</v>
       </c>
@@ -9454,8 +9712,8 @@
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A86">
-        <v>42</v>
+      <c r="A86" t="s">
+        <v>1455</v>
       </c>
       <c r="B86" t="s">
         <v>712</v>
@@ -9469,6 +9727,9 @@
       <c r="E86" t="s">
         <v>949</v>
       </c>
+      <c r="F86" t="s">
+        <v>1454</v>
+      </c>
       <c r="G86" t="s">
         <v>716</v>
       </c>
@@ -9486,8 +9747,8 @@
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A87">
-        <v>43</v>
+      <c r="A87" t="s">
+        <v>1455</v>
       </c>
       <c r="B87" t="s">
         <v>712</v>
@@ -9501,6 +9762,9 @@
       <c r="E87" t="s">
         <v>952</v>
       </c>
+      <c r="F87" t="s">
+        <v>1454</v>
+      </c>
       <c r="G87" t="s">
         <v>716</v>
       </c>
@@ -9518,8 +9782,8 @@
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A88">
-        <v>42</v>
+      <c r="A88" t="s">
+        <v>1455</v>
       </c>
       <c r="B88" t="s">
         <v>703</v>
@@ -9533,6 +9797,9 @@
       <c r="E88" t="s">
         <v>955</v>
       </c>
+      <c r="F88" t="s">
+        <v>1454</v>
+      </c>
       <c r="G88" t="s">
         <v>723</v>
       </c>
@@ -9547,8 +9814,8 @@
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A89">
-        <v>44</v>
+      <c r="A89" t="s">
+        <v>1455</v>
       </c>
       <c r="B89" t="s">
         <v>712</v>
@@ -9562,6 +9829,9 @@
       <c r="E89" t="s">
         <v>958</v>
       </c>
+      <c r="F89" t="s">
+        <v>1454</v>
+      </c>
       <c r="G89" t="s">
         <v>716</v>
       </c>
@@ -9579,8 +9849,8 @@
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A90">
-        <v>43</v>
+      <c r="A90" t="s">
+        <v>1455</v>
       </c>
       <c r="B90" t="s">
         <v>703</v>
@@ -9594,6 +9864,9 @@
       <c r="E90" t="s">
         <v>960</v>
       </c>
+      <c r="F90" t="s">
+        <v>1454</v>
+      </c>
       <c r="G90" t="s">
         <v>723</v>
       </c>
@@ -9611,8 +9884,8 @@
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A91">
-        <v>45</v>
+      <c r="A91" t="s">
+        <v>1455</v>
       </c>
       <c r="B91" t="s">
         <v>712</v>
@@ -9626,6 +9899,9 @@
       <c r="E91" t="s">
         <v>963</v>
       </c>
+      <c r="F91" t="s">
+        <v>1454</v>
+      </c>
       <c r="G91" t="s">
         <v>716</v>
       </c>
@@ -9643,8 +9919,8 @@
       </c>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A92">
-        <v>44</v>
+      <c r="A92" t="s">
+        <v>1455</v>
       </c>
       <c r="B92" t="s">
         <v>703</v>
@@ -9658,6 +9934,9 @@
       <c r="E92" t="s">
         <v>966</v>
       </c>
+      <c r="F92" t="s">
+        <v>1454</v>
+      </c>
       <c r="G92" t="s">
         <v>723</v>
       </c>
@@ -9675,8 +9954,8 @@
       </c>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A93">
-        <v>46</v>
+      <c r="A93" t="s">
+        <v>1455</v>
       </c>
       <c r="B93" t="s">
         <v>712</v>
@@ -9690,6 +9969,9 @@
       <c r="E93" t="s">
         <v>968</v>
       </c>
+      <c r="F93" t="s">
+        <v>1454</v>
+      </c>
       <c r="G93" t="s">
         <v>734</v>
       </c>
@@ -9704,8 +9986,8 @@
       </c>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A94">
-        <v>45</v>
+      <c r="A94" t="s">
+        <v>1455</v>
       </c>
       <c r="B94" t="s">
         <v>703</v>
@@ -9719,6 +10001,9 @@
       <c r="E94" t="s">
         <v>972</v>
       </c>
+      <c r="F94" t="s">
+        <v>1454</v>
+      </c>
       <c r="G94" t="s">
         <v>723</v>
       </c>
@@ -9733,8 +10018,8 @@
       </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A95">
-        <v>1</v>
+      <c r="A95" t="s">
+        <v>1455</v>
       </c>
       <c r="B95" t="s">
         <v>973</v>
@@ -9748,10 +10033,13 @@
       <c r="E95" t="s">
         <v>974</v>
       </c>
+      <c r="F95" t="s">
+        <v>1454</v>
+      </c>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A96">
-        <v>1</v>
+      <c r="A96" t="s">
+        <v>1455</v>
       </c>
       <c r="B96" t="s">
         <v>975</v>
@@ -9765,10 +10053,13 @@
       <c r="E96" t="s">
         <v>976</v>
       </c>
+      <c r="F96" t="s">
+        <v>1454</v>
+      </c>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A97">
-        <v>2</v>
+      <c r="A97" t="s">
+        <v>1455</v>
       </c>
       <c r="B97" t="s">
         <v>702</v>
@@ -9782,10 +10073,13 @@
       <c r="E97" t="s">
         <v>976</v>
       </c>
+      <c r="F97" t="s">
+        <v>1454</v>
+      </c>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A98">
-        <v>47</v>
+      <c r="A98" t="s">
+        <v>1455</v>
       </c>
       <c r="B98" t="s">
         <v>712</v>
@@ -9799,6 +10093,9 @@
       <c r="E98" t="s">
         <v>979</v>
       </c>
+      <c r="F98" t="s">
+        <v>1454</v>
+      </c>
       <c r="G98" t="s">
         <v>980</v>
       </c>
@@ -9816,8 +10113,8 @@
       </c>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A99">
-        <v>46</v>
+      <c r="A99" t="s">
+        <v>1455</v>
       </c>
       <c r="B99" t="s">
         <v>703</v>
@@ -9831,6 +10128,9 @@
       <c r="E99" t="s">
         <v>984</v>
       </c>
+      <c r="F99" t="s">
+        <v>1454</v>
+      </c>
       <c r="G99" t="s">
         <v>981</v>
       </c>
@@ -9848,8 +10148,8 @@
       </c>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A100">
-        <v>48</v>
+      <c r="A100" t="s">
+        <v>1455</v>
       </c>
       <c r="B100" t="s">
         <v>712</v>
@@ -9863,6 +10163,9 @@
       <c r="E100" t="s">
         <v>986</v>
       </c>
+      <c r="F100" t="s">
+        <v>1454</v>
+      </c>
       <c r="G100" t="s">
         <v>980</v>
       </c>
@@ -9880,8 +10183,8 @@
       </c>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A101">
-        <v>47</v>
+      <c r="A101" t="s">
+        <v>1455</v>
       </c>
       <c r="B101" t="s">
         <v>703</v>
@@ -9895,6 +10198,9 @@
       <c r="E101" t="s">
         <v>989</v>
       </c>
+      <c r="F101" t="s">
+        <v>1454</v>
+      </c>
       <c r="G101" t="s">
         <v>990</v>
       </c>
@@ -9912,8 +10218,8 @@
       </c>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A102">
-        <v>49</v>
+      <c r="A102" t="s">
+        <v>1455</v>
       </c>
       <c r="B102" t="s">
         <v>712</v>
@@ -9927,6 +10233,9 @@
       <c r="E102" t="s">
         <v>993</v>
       </c>
+      <c r="F102" t="s">
+        <v>1454</v>
+      </c>
       <c r="G102" t="s">
         <v>994</v>
       </c>
@@ -9944,8 +10253,8 @@
       </c>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A103">
-        <v>48</v>
+      <c r="A103" t="s">
+        <v>1455</v>
       </c>
       <c r="B103" t="s">
         <v>703</v>
@@ -9959,6 +10268,9 @@
       <c r="E103" t="s">
         <v>996</v>
       </c>
+      <c r="F103" t="s">
+        <v>1454</v>
+      </c>
       <c r="G103" t="s">
         <v>997</v>
       </c>
@@ -9973,8 +10285,8 @@
       </c>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A104">
-        <v>50</v>
+      <c r="A104" t="s">
+        <v>1455</v>
       </c>
       <c r="B104" t="s">
         <v>712</v>
@@ -9988,6 +10300,9 @@
       <c r="E104" t="s">
         <v>1000</v>
       </c>
+      <c r="F104" t="s">
+        <v>1454</v>
+      </c>
       <c r="G104" t="s">
         <v>980</v>
       </c>
@@ -10005,8 +10320,8 @@
       </c>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A105">
-        <v>49</v>
+      <c r="A105" t="s">
+        <v>1455</v>
       </c>
       <c r="B105" t="s">
         <v>703</v>
@@ -10020,6 +10335,9 @@
       <c r="E105" t="s">
         <v>1003</v>
       </c>
+      <c r="F105" t="s">
+        <v>1454</v>
+      </c>
       <c r="G105" t="s">
         <v>981</v>
       </c>
@@ -10037,8 +10355,8 @@
       </c>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A106">
-        <v>51</v>
+      <c r="A106" t="s">
+        <v>1455</v>
       </c>
       <c r="B106" t="s">
         <v>712</v>
@@ -10052,6 +10370,9 @@
       <c r="E106" t="s">
         <v>1005</v>
       </c>
+      <c r="F106" t="s">
+        <v>1454</v>
+      </c>
       <c r="G106" t="s">
         <v>994</v>
       </c>
@@ -10069,8 +10390,8 @@
       </c>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A107">
-        <v>50</v>
+      <c r="A107" t="s">
+        <v>1455</v>
       </c>
       <c r="B107" t="s">
         <v>703</v>
@@ -10084,6 +10405,9 @@
       <c r="E107" t="s">
         <v>1008</v>
       </c>
+      <c r="F107" t="s">
+        <v>1454</v>
+      </c>
       <c r="G107" t="s">
         <v>990</v>
       </c>
@@ -10101,8 +10425,8 @@
       </c>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A108">
-        <v>52</v>
+      <c r="A108" t="s">
+        <v>1455</v>
       </c>
       <c r="B108" t="s">
         <v>712</v>
@@ -10116,6 +10440,9 @@
       <c r="E108" t="s">
         <v>1011</v>
       </c>
+      <c r="F108" t="s">
+        <v>1454</v>
+      </c>
       <c r="G108" t="s">
         <v>980</v>
       </c>
@@ -10133,8 +10460,8 @@
       </c>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A109">
-        <v>51</v>
+      <c r="A109" t="s">
+        <v>1455</v>
       </c>
       <c r="B109" t="s">
         <v>703</v>
@@ -10148,6 +10475,9 @@
       <c r="E109" t="s">
         <v>1014</v>
       </c>
+      <c r="F109" t="s">
+        <v>1454</v>
+      </c>
       <c r="G109" t="s">
         <v>981</v>
       </c>
@@ -10165,8 +10495,8 @@
       </c>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A110">
-        <v>53</v>
+      <c r="A110" t="s">
+        <v>1455</v>
       </c>
       <c r="B110" t="s">
         <v>712</v>
@@ -10180,6 +10510,9 @@
       <c r="E110" t="s">
         <v>1017</v>
       </c>
+      <c r="F110" t="s">
+        <v>1454</v>
+      </c>
       <c r="G110" t="s">
         <v>994</v>
       </c>
@@ -10197,8 +10530,8 @@
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A111">
-        <v>52</v>
+      <c r="A111" t="s">
+        <v>1455</v>
       </c>
       <c r="B111" t="s">
         <v>703</v>
@@ -10212,6 +10545,9 @@
       <c r="E111" t="s">
         <v>1020</v>
       </c>
+      <c r="F111" t="s">
+        <v>1454</v>
+      </c>
       <c r="G111" t="s">
         <v>990</v>
       </c>
@@ -10229,8 +10565,8 @@
       </c>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A112">
-        <v>54</v>
+      <c r="A112" t="s">
+        <v>1455</v>
       </c>
       <c r="B112" t="s">
         <v>712</v>
@@ -10244,6 +10580,9 @@
       <c r="E112" t="s">
         <v>1022</v>
       </c>
+      <c r="F112" t="s">
+        <v>1454</v>
+      </c>
       <c r="G112" t="s">
         <v>980</v>
       </c>
@@ -10261,8 +10600,8 @@
       </c>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A113">
-        <v>53</v>
+      <c r="A113" t="s">
+        <v>1455</v>
       </c>
       <c r="B113" t="s">
         <v>703</v>
@@ -10276,6 +10615,9 @@
       <c r="E113" t="s">
         <v>1025</v>
       </c>
+      <c r="F113" t="s">
+        <v>1454</v>
+      </c>
       <c r="G113" t="s">
         <v>981</v>
       </c>
@@ -10293,8 +10635,8 @@
       </c>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A114">
-        <v>55</v>
+      <c r="A114" t="s">
+        <v>1455</v>
       </c>
       <c r="B114" t="s">
         <v>712</v>
@@ -10308,6 +10650,9 @@
       <c r="E114" t="s">
         <v>1028</v>
       </c>
+      <c r="F114" t="s">
+        <v>1454</v>
+      </c>
       <c r="G114" t="s">
         <v>994</v>
       </c>
@@ -10325,8 +10670,8 @@
       </c>
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A115">
-        <v>54</v>
+      <c r="A115" t="s">
+        <v>1455</v>
       </c>
       <c r="B115" t="s">
         <v>703</v>
@@ -10340,6 +10685,9 @@
       <c r="E115" t="s">
         <v>1031</v>
       </c>
+      <c r="F115" t="s">
+        <v>1454</v>
+      </c>
       <c r="G115" t="s">
         <v>981</v>
       </c>
@@ -10357,8 +10705,8 @@
       </c>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A116">
-        <v>56</v>
+      <c r="A116" t="s">
+        <v>1455</v>
       </c>
       <c r="B116" t="s">
         <v>712</v>
@@ -10372,6 +10720,9 @@
       <c r="E116" t="s">
         <v>1033</v>
       </c>
+      <c r="F116" t="s">
+        <v>1454</v>
+      </c>
       <c r="G116" t="s">
         <v>994</v>
       </c>
@@ -10386,8 +10737,8 @@
       </c>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A117">
-        <v>55</v>
+      <c r="A117" t="s">
+        <v>1455</v>
       </c>
       <c r="B117" t="s">
         <v>703</v>
@@ -10401,6 +10752,9 @@
       <c r="E117" t="s">
         <v>1036</v>
       </c>
+      <c r="F117" t="s">
+        <v>1454</v>
+      </c>
       <c r="G117" t="s">
         <v>990</v>
       </c>
@@ -10418,8 +10772,8 @@
       </c>
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A118">
-        <v>57</v>
+      <c r="A118" t="s">
+        <v>1455</v>
       </c>
       <c r="B118" t="s">
         <v>712</v>
@@ -10433,6 +10787,9 @@
       <c r="E118" t="s">
         <v>1039</v>
       </c>
+      <c r="F118" t="s">
+        <v>1454</v>
+      </c>
       <c r="G118" t="s">
         <v>980</v>
       </c>
@@ -10450,8 +10807,8 @@
       </c>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A119">
-        <v>56</v>
+      <c r="A119" t="s">
+        <v>1455</v>
       </c>
       <c r="B119" t="s">
         <v>703</v>
@@ -10465,6 +10822,9 @@
       <c r="E119" t="s">
         <v>1042</v>
       </c>
+      <c r="F119" t="s">
+        <v>1454</v>
+      </c>
       <c r="G119" t="s">
         <v>981</v>
       </c>
@@ -10482,8 +10842,8 @@
       </c>
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A120">
-        <v>58</v>
+      <c r="A120" t="s">
+        <v>1455</v>
       </c>
       <c r="B120" t="s">
         <v>712</v>
@@ -10497,6 +10857,9 @@
       <c r="E120" t="s">
         <v>1045</v>
       </c>
+      <c r="F120" t="s">
+        <v>1454</v>
+      </c>
       <c r="G120" t="s">
         <v>994</v>
       </c>
@@ -10514,8 +10877,8 @@
       </c>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A121">
-        <v>57</v>
+      <c r="A121" t="s">
+        <v>1455</v>
       </c>
       <c r="B121" t="s">
         <v>703</v>
@@ -10529,6 +10892,9 @@
       <c r="E121" t="s">
         <v>1047</v>
       </c>
+      <c r="F121" t="s">
+        <v>1454</v>
+      </c>
       <c r="G121" t="s">
         <v>997</v>
       </c>
@@ -10546,8 +10912,8 @@
       </c>
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A122">
-        <v>59</v>
+      <c r="A122" t="s">
+        <v>1455</v>
       </c>
       <c r="B122" t="s">
         <v>712</v>
@@ -10561,6 +10927,9 @@
       <c r="E122" t="s">
         <v>1050</v>
       </c>
+      <c r="F122" t="s">
+        <v>1454</v>
+      </c>
       <c r="G122" t="s">
         <v>980</v>
       </c>
@@ -10578,8 +10947,8 @@
       </c>
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A123">
-        <v>58</v>
+      <c r="A123" t="s">
+        <v>1455</v>
       </c>
       <c r="B123" t="s">
         <v>703</v>
@@ -10593,6 +10962,9 @@
       <c r="E123" t="s">
         <v>1052</v>
       </c>
+      <c r="F123" t="s">
+        <v>1454</v>
+      </c>
       <c r="G123" t="s">
         <v>981</v>
       </c>
@@ -10610,8 +10982,8 @@
       </c>
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A124">
-        <v>60</v>
+      <c r="A124" t="s">
+        <v>1455</v>
       </c>
       <c r="B124" t="s">
         <v>712</v>
@@ -10625,6 +10997,9 @@
       <c r="E124" t="s">
         <v>1054</v>
       </c>
+      <c r="F124" t="s">
+        <v>1454</v>
+      </c>
       <c r="G124" t="s">
         <v>994</v>
       </c>
@@ -10642,8 +11017,8 @@
       </c>
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A125">
-        <v>59</v>
+      <c r="A125" t="s">
+        <v>1455</v>
       </c>
       <c r="B125" t="s">
         <v>703</v>
@@ -10657,6 +11032,9 @@
       <c r="E125" t="s">
         <v>1056</v>
       </c>
+      <c r="F125" t="s">
+        <v>1454</v>
+      </c>
       <c r="G125" t="s">
         <v>981</v>
       </c>
@@ -10674,8 +11052,8 @@
       </c>
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A126">
-        <v>61</v>
+      <c r="A126" t="s">
+        <v>1455</v>
       </c>
       <c r="B126" t="s">
         <v>712</v>
@@ -10689,6 +11067,9 @@
       <c r="E126" t="s">
         <v>1059</v>
       </c>
+      <c r="F126" t="s">
+        <v>1454</v>
+      </c>
       <c r="G126" t="s">
         <v>980</v>
       </c>
@@ -10706,8 +11087,8 @@
       </c>
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A127">
-        <v>60</v>
+      <c r="A127" t="s">
+        <v>1455</v>
       </c>
       <c r="B127" t="s">
         <v>703</v>
@@ -10721,6 +11102,9 @@
       <c r="E127" t="s">
         <v>1062</v>
       </c>
+      <c r="F127" t="s">
+        <v>1454</v>
+      </c>
       <c r="G127" t="s">
         <v>990</v>
       </c>
@@ -10738,8 +11122,8 @@
       </c>
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A128">
-        <v>62</v>
+      <c r="A128" t="s">
+        <v>1455</v>
       </c>
       <c r="B128" t="s">
         <v>712</v>
@@ -10753,6 +11137,9 @@
       <c r="E128" t="s">
         <v>1065</v>
       </c>
+      <c r="F128" t="s">
+        <v>1454</v>
+      </c>
       <c r="G128" t="s">
         <v>980</v>
       </c>
@@ -10770,8 +11157,8 @@
       </c>
     </row>
     <row r="129" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A129">
-        <v>61</v>
+      <c r="A129" t="s">
+        <v>1455</v>
       </c>
       <c r="B129" t="s">
         <v>703</v>
@@ -10785,6 +11172,9 @@
       <c r="E129" t="s">
         <v>1067</v>
       </c>
+      <c r="F129" t="s">
+        <v>1454</v>
+      </c>
       <c r="G129" t="s">
         <v>990</v>
       </c>
@@ -10802,8 +11192,8 @@
       </c>
     </row>
     <row r="130" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A130">
-        <v>63</v>
+      <c r="A130" t="s">
+        <v>1455</v>
       </c>
       <c r="B130" t="s">
         <v>712</v>
@@ -10817,6 +11207,9 @@
       <c r="E130" t="s">
         <v>1070</v>
       </c>
+      <c r="F130" t="s">
+        <v>1454</v>
+      </c>
       <c r="G130" t="s">
         <v>994</v>
       </c>
@@ -10834,8 +11227,8 @@
       </c>
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A131">
-        <v>62</v>
+      <c r="A131" t="s">
+        <v>1455</v>
       </c>
       <c r="B131" t="s">
         <v>703</v>
@@ -10849,6 +11242,9 @@
       <c r="E131" t="s">
         <v>1072</v>
       </c>
+      <c r="F131" t="s">
+        <v>1454</v>
+      </c>
       <c r="G131" t="s">
         <v>981</v>
       </c>
@@ -10866,8 +11262,8 @@
       </c>
     </row>
     <row r="132" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A132">
-        <v>64</v>
+      <c r="A132" t="s">
+        <v>1455</v>
       </c>
       <c r="B132" t="s">
         <v>712</v>
@@ -10881,6 +11277,9 @@
       <c r="E132" t="s">
         <v>1075</v>
       </c>
+      <c r="F132" t="s">
+        <v>1454</v>
+      </c>
       <c r="G132" t="s">
         <v>980</v>
       </c>
@@ -10898,8 +11297,8 @@
       </c>
     </row>
     <row r="133" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A133">
-        <v>63</v>
+      <c r="A133" t="s">
+        <v>1455</v>
       </c>
       <c r="B133" t="s">
         <v>703</v>
@@ -10913,6 +11312,9 @@
       <c r="E133" t="s">
         <v>1078</v>
       </c>
+      <c r="F133" t="s">
+        <v>1454</v>
+      </c>
       <c r="G133" t="s">
         <v>981</v>
       </c>
@@ -10930,8 +11332,8 @@
       </c>
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A134">
-        <v>65</v>
+      <c r="A134" t="s">
+        <v>1455</v>
       </c>
       <c r="B134" t="s">
         <v>712</v>
@@ -10945,6 +11347,9 @@
       <c r="E134" t="s">
         <v>1081</v>
       </c>
+      <c r="F134" t="s">
+        <v>1454</v>
+      </c>
       <c r="G134" t="s">
         <v>994</v>
       </c>
@@ -10962,8 +11367,8 @@
       </c>
     </row>
     <row r="135" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A135">
-        <v>64</v>
+      <c r="A135" t="s">
+        <v>1455</v>
       </c>
       <c r="B135" t="s">
         <v>703</v>
@@ -10977,6 +11382,9 @@
       <c r="E135" t="s">
         <v>1083</v>
       </c>
+      <c r="F135" t="s">
+        <v>1454</v>
+      </c>
       <c r="G135" t="s">
         <v>990</v>
       </c>
@@ -10994,8 +11402,8 @@
       </c>
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A136">
-        <v>66</v>
+      <c r="A136" t="s">
+        <v>1455</v>
       </c>
       <c r="B136" t="s">
         <v>712</v>
@@ -11009,6 +11417,9 @@
       <c r="E136" t="s">
         <v>1085</v>
       </c>
+      <c r="F136" t="s">
+        <v>1454</v>
+      </c>
       <c r="G136" t="s">
         <v>994</v>
       </c>
@@ -11026,8 +11437,8 @@
       </c>
     </row>
     <row r="137" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A137">
-        <v>65</v>
+      <c r="A137" t="s">
+        <v>1455</v>
       </c>
       <c r="B137" t="s">
         <v>703</v>
@@ -11041,6 +11452,9 @@
       <c r="E137" t="s">
         <v>1087</v>
       </c>
+      <c r="F137" t="s">
+        <v>1454</v>
+      </c>
       <c r="G137" t="s">
         <v>990</v>
       </c>
@@ -11058,8 +11472,8 @@
       </c>
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A138">
-        <v>67</v>
+      <c r="A138" t="s">
+        <v>1455</v>
       </c>
       <c r="B138" t="s">
         <v>712</v>
@@ -11073,6 +11487,9 @@
       <c r="E138" t="s">
         <v>1089</v>
       </c>
+      <c r="F138" t="s">
+        <v>1454</v>
+      </c>
       <c r="G138" t="s">
         <v>980</v>
       </c>
@@ -11090,8 +11507,8 @@
       </c>
     </row>
     <row r="139" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A139">
-        <v>66</v>
+      <c r="A139" t="s">
+        <v>1455</v>
       </c>
       <c r="B139" t="s">
         <v>703</v>
@@ -11105,6 +11522,9 @@
       <c r="E139" t="s">
         <v>1091</v>
       </c>
+      <c r="F139" t="s">
+        <v>1454</v>
+      </c>
       <c r="G139" t="s">
         <v>981</v>
       </c>
@@ -11122,8 +11542,8 @@
       </c>
     </row>
     <row r="140" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A140">
-        <v>68</v>
+      <c r="A140" t="s">
+        <v>1455</v>
       </c>
       <c r="B140" t="s">
         <v>712</v>
@@ -11137,6 +11557,9 @@
       <c r="E140" t="s">
         <v>1094</v>
       </c>
+      <c r="F140" t="s">
+        <v>1454</v>
+      </c>
       <c r="G140" t="s">
         <v>994</v>
       </c>
@@ -11154,8 +11577,8 @@
       </c>
     </row>
     <row r="141" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A141">
-        <v>67</v>
+      <c r="A141" t="s">
+        <v>1455</v>
       </c>
       <c r="B141" t="s">
         <v>703</v>
@@ -11169,6 +11592,9 @@
       <c r="E141" t="s">
         <v>1097</v>
       </c>
+      <c r="F141" t="s">
+        <v>1454</v>
+      </c>
       <c r="G141" t="s">
         <v>990</v>
       </c>
@@ -11186,8 +11612,8 @@
       </c>
     </row>
     <row r="142" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A142">
-        <v>69</v>
+      <c r="A142" t="s">
+        <v>1455</v>
       </c>
       <c r="B142" t="s">
         <v>712</v>
@@ -11201,6 +11627,9 @@
       <c r="E142" t="s">
         <v>1100</v>
       </c>
+      <c r="F142" t="s">
+        <v>1454</v>
+      </c>
       <c r="G142" t="s">
         <v>980</v>
       </c>
@@ -11218,8 +11647,8 @@
       </c>
     </row>
     <row r="143" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A143">
-        <v>68</v>
+      <c r="A143" t="s">
+        <v>1455</v>
       </c>
       <c r="B143" t="s">
         <v>703</v>
@@ -11233,6 +11662,9 @@
       <c r="E143" t="s">
         <v>1102</v>
       </c>
+      <c r="F143" t="s">
+        <v>1454</v>
+      </c>
       <c r="G143" t="s">
         <v>981</v>
       </c>
@@ -11250,8 +11682,8 @@
       </c>
     </row>
     <row r="144" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A144">
-        <v>70</v>
+      <c r="A144" t="s">
+        <v>1455</v>
       </c>
       <c r="B144" t="s">
         <v>712</v>
@@ -11265,6 +11697,9 @@
       <c r="E144" t="s">
         <v>1105</v>
       </c>
+      <c r="F144" t="s">
+        <v>1454</v>
+      </c>
       <c r="G144" t="s">
         <v>994</v>
       </c>
@@ -11282,8 +11717,8 @@
       </c>
     </row>
     <row r="145" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A145">
-        <v>69</v>
+      <c r="A145" t="s">
+        <v>1455</v>
       </c>
       <c r="B145" t="s">
         <v>703</v>
@@ -11297,6 +11732,9 @@
       <c r="E145" t="s">
         <v>1107</v>
       </c>
+      <c r="F145" t="s">
+        <v>1454</v>
+      </c>
       <c r="G145" t="s">
         <v>997</v>
       </c>
@@ -11314,8 +11752,8 @@
       </c>
     </row>
     <row r="146" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A146">
-        <v>71</v>
+      <c r="A146" t="s">
+        <v>1455</v>
       </c>
       <c r="B146" t="s">
         <v>712</v>
@@ -11329,6 +11767,9 @@
       <c r="E146" t="s">
         <v>1110</v>
       </c>
+      <c r="F146" t="s">
+        <v>1454</v>
+      </c>
       <c r="G146" t="s">
         <v>980</v>
       </c>
@@ -11346,8 +11787,8 @@
       </c>
     </row>
     <row r="147" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A147">
-        <v>70</v>
+      <c r="A147" t="s">
+        <v>1455</v>
       </c>
       <c r="B147" t="s">
         <v>703</v>
@@ -11361,6 +11802,9 @@
       <c r="E147" t="s">
         <v>1113</v>
       </c>
+      <c r="F147" t="s">
+        <v>1454</v>
+      </c>
       <c r="G147" t="s">
         <v>981</v>
       </c>
@@ -11378,8 +11822,8 @@
       </c>
     </row>
     <row r="148" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A148">
-        <v>72</v>
+      <c r="A148" t="s">
+        <v>1455</v>
       </c>
       <c r="B148" t="s">
         <v>712</v>
@@ -11393,6 +11837,9 @@
       <c r="E148" t="s">
         <v>1116</v>
       </c>
+      <c r="F148" t="s">
+        <v>1454</v>
+      </c>
       <c r="G148" t="s">
         <v>994</v>
       </c>
@@ -11410,8 +11857,8 @@
       </c>
     </row>
     <row r="149" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A149">
-        <v>71</v>
+      <c r="A149" t="s">
+        <v>1455</v>
       </c>
       <c r="B149" t="s">
         <v>703</v>
@@ -11425,6 +11872,9 @@
       <c r="E149" t="s">
         <v>1117</v>
       </c>
+      <c r="F149" t="s">
+        <v>1454</v>
+      </c>
       <c r="G149" t="s">
         <v>990</v>
       </c>
@@ -11442,8 +11892,8 @@
       </c>
     </row>
     <row r="150" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A150">
-        <v>73</v>
+      <c r="A150" t="s">
+        <v>1455</v>
       </c>
       <c r="B150" t="s">
         <v>712</v>
@@ -11457,6 +11907,9 @@
       <c r="E150" t="s">
         <v>1120</v>
       </c>
+      <c r="F150" t="s">
+        <v>1454</v>
+      </c>
       <c r="G150" t="s">
         <v>980</v>
       </c>
@@ -11474,8 +11927,8 @@
       </c>
     </row>
     <row r="151" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A151">
-        <v>72</v>
+      <c r="A151" t="s">
+        <v>1455</v>
       </c>
       <c r="B151" t="s">
         <v>703</v>
@@ -11489,6 +11942,9 @@
       <c r="E151" t="s">
         <v>1123</v>
       </c>
+      <c r="F151" t="s">
+        <v>1454</v>
+      </c>
       <c r="G151" t="s">
         <v>981</v>
       </c>
@@ -11506,8 +11962,8 @@
       </c>
     </row>
     <row r="152" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A152">
-        <v>74</v>
+      <c r="A152" t="s">
+        <v>1455</v>
       </c>
       <c r="B152" t="s">
         <v>712</v>
@@ -11521,6 +11977,9 @@
       <c r="E152" t="s">
         <v>1126</v>
       </c>
+      <c r="F152" t="s">
+        <v>1454</v>
+      </c>
       <c r="G152" t="s">
         <v>711</v>
       </c>
@@ -11538,8 +11997,8 @@
       </c>
     </row>
     <row r="153" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A153">
-        <v>73</v>
+      <c r="A153" t="s">
+        <v>1455</v>
       </c>
       <c r="B153" t="s">
         <v>703</v>
@@ -11553,6 +12012,9 @@
       <c r="E153" t="s">
         <v>1129</v>
       </c>
+      <c r="F153" t="s">
+        <v>1454</v>
+      </c>
       <c r="G153" t="s">
         <v>990</v>
       </c>
@@ -11570,8 +12032,8 @@
       </c>
     </row>
     <row r="154" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A154">
-        <v>75</v>
+      <c r="A154" t="s">
+        <v>1455</v>
       </c>
       <c r="B154" t="s">
         <v>712</v>
@@ -11585,6 +12047,9 @@
       <c r="E154" t="s">
         <v>1132</v>
       </c>
+      <c r="F154" t="s">
+        <v>1454</v>
+      </c>
       <c r="G154" t="s">
         <v>980</v>
       </c>
@@ -11602,8 +12067,8 @@
       </c>
     </row>
     <row r="155" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A155">
-        <v>74</v>
+      <c r="A155" t="s">
+        <v>1455</v>
       </c>
       <c r="B155" t="s">
         <v>703</v>
@@ -11617,6 +12082,9 @@
       <c r="E155" t="s">
         <v>1135</v>
       </c>
+      <c r="F155" t="s">
+        <v>1454</v>
+      </c>
       <c r="G155" t="s">
         <v>981</v>
       </c>
@@ -11634,8 +12102,8 @@
       </c>
     </row>
     <row r="156" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A156">
-        <v>76</v>
+      <c r="A156" t="s">
+        <v>1455</v>
       </c>
       <c r="B156" t="s">
         <v>712</v>
@@ -11649,6 +12117,9 @@
       <c r="E156" t="s">
         <v>1137</v>
       </c>
+      <c r="F156" t="s">
+        <v>1454</v>
+      </c>
       <c r="G156" t="s">
         <v>994</v>
       </c>
@@ -11666,8 +12137,8 @@
       </c>
     </row>
     <row r="157" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A157">
-        <v>75</v>
+      <c r="A157" t="s">
+        <v>1455</v>
       </c>
       <c r="B157" t="s">
         <v>703</v>
@@ -11681,6 +12152,9 @@
       <c r="E157" t="s">
         <v>1140</v>
       </c>
+      <c r="F157" t="s">
+        <v>1454</v>
+      </c>
       <c r="G157" t="s">
         <v>990</v>
       </c>
@@ -11698,8 +12172,8 @@
       </c>
     </row>
     <row r="158" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A158">
-        <v>77</v>
+      <c r="A158" t="s">
+        <v>1455</v>
       </c>
       <c r="B158" t="s">
         <v>712</v>
@@ -11713,6 +12187,9 @@
       <c r="E158" t="s">
         <v>1143</v>
       </c>
+      <c r="F158" t="s">
+        <v>1454</v>
+      </c>
       <c r="G158" t="s">
         <v>711</v>
       </c>
@@ -11730,8 +12207,8 @@
       </c>
     </row>
     <row r="159" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A159">
-        <v>76</v>
+      <c r="A159" t="s">
+        <v>1455</v>
       </c>
       <c r="B159" t="s">
         <v>703</v>
@@ -11745,6 +12222,9 @@
       <c r="E159" t="s">
         <v>1146</v>
       </c>
+      <c r="F159" t="s">
+        <v>1454</v>
+      </c>
       <c r="G159" t="s">
         <v>981</v>
       </c>
@@ -11762,8 +12242,8 @@
       </c>
     </row>
     <row r="160" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A160">
-        <v>78</v>
+      <c r="A160" t="s">
+        <v>1455</v>
       </c>
       <c r="B160" t="s">
         <v>712</v>
@@ -11777,6 +12257,9 @@
       <c r="E160" t="s">
         <v>1149</v>
       </c>
+      <c r="F160" t="s">
+        <v>1454</v>
+      </c>
       <c r="G160" t="s">
         <v>994</v>
       </c>
@@ -11794,8 +12277,8 @@
       </c>
     </row>
     <row r="161" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A161">
-        <v>77</v>
+      <c r="A161" t="s">
+        <v>1455</v>
       </c>
       <c r="B161" t="s">
         <v>703</v>
@@ -11809,6 +12292,9 @@
       <c r="E161" t="s">
         <v>1151</v>
       </c>
+      <c r="F161" t="s">
+        <v>1454</v>
+      </c>
       <c r="G161" t="s">
         <v>990</v>
       </c>
@@ -11826,8 +12312,8 @@
       </c>
     </row>
     <row r="162" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A162">
-        <v>79</v>
+      <c r="A162" t="s">
+        <v>1455</v>
       </c>
       <c r="B162" t="s">
         <v>712</v>
@@ -11841,6 +12327,9 @@
       <c r="E162" t="s">
         <v>1154</v>
       </c>
+      <c r="F162" t="s">
+        <v>1454</v>
+      </c>
       <c r="G162" t="s">
         <v>980</v>
       </c>
@@ -11858,8 +12347,8 @@
       </c>
     </row>
     <row r="163" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A163">
-        <v>78</v>
+      <c r="A163" t="s">
+        <v>1455</v>
       </c>
       <c r="B163" t="s">
         <v>703</v>
@@ -11873,6 +12362,9 @@
       <c r="E163" t="s">
         <v>1155</v>
       </c>
+      <c r="F163" t="s">
+        <v>1454</v>
+      </c>
       <c r="G163" t="s">
         <v>981</v>
       </c>
@@ -11890,8 +12382,8 @@
       </c>
     </row>
     <row r="164" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A164">
-        <v>80</v>
+      <c r="A164" t="s">
+        <v>1455</v>
       </c>
       <c r="B164" t="s">
         <v>712</v>
@@ -11905,6 +12397,9 @@
       <c r="E164" t="s">
         <v>1158</v>
       </c>
+      <c r="F164" t="s">
+        <v>1454</v>
+      </c>
       <c r="G164" t="s">
         <v>994</v>
       </c>
@@ -11922,8 +12417,8 @@
       </c>
     </row>
     <row r="165" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A165">
-        <v>79</v>
+      <c r="A165" t="s">
+        <v>1455</v>
       </c>
       <c r="B165" t="s">
         <v>703</v>
@@ -11937,6 +12432,9 @@
       <c r="E165" t="s">
         <v>1160</v>
       </c>
+      <c r="F165" t="s">
+        <v>1454</v>
+      </c>
       <c r="G165" t="s">
         <v>981</v>
       </c>
@@ -11954,8 +12452,8 @@
       </c>
     </row>
     <row r="166" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A166">
-        <v>81</v>
+      <c r="A166" t="s">
+        <v>1455</v>
       </c>
       <c r="B166" t="s">
         <v>712</v>
@@ -11969,6 +12467,9 @@
       <c r="E166" t="s">
         <v>1163</v>
       </c>
+      <c r="F166" t="s">
+        <v>1454</v>
+      </c>
       <c r="G166" t="s">
         <v>980</v>
       </c>
@@ -11986,8 +12487,8 @@
       </c>
     </row>
     <row r="167" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A167">
-        <v>80</v>
+      <c r="A167" t="s">
+        <v>1455</v>
       </c>
       <c r="B167" t="s">
         <v>703</v>
@@ -12001,6 +12502,9 @@
       <c r="E167" t="s">
         <v>1165</v>
       </c>
+      <c r="F167" t="s">
+        <v>1454</v>
+      </c>
       <c r="G167" t="s">
         <v>990</v>
       </c>
@@ -12018,8 +12522,8 @@
       </c>
     </row>
     <row r="168" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A168">
-        <v>82</v>
+      <c r="A168" t="s">
+        <v>1455</v>
       </c>
       <c r="B168" t="s">
         <v>712</v>
@@ -12033,6 +12537,9 @@
       <c r="E168" t="s">
         <v>1168</v>
       </c>
+      <c r="F168" t="s">
+        <v>1454</v>
+      </c>
       <c r="G168" t="s">
         <v>994</v>
       </c>
@@ -12050,8 +12557,8 @@
       </c>
     </row>
     <row r="169" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A169">
-        <v>81</v>
+      <c r="A169" t="s">
+        <v>1455</v>
       </c>
       <c r="B169" t="s">
         <v>703</v>
@@ -12065,6 +12572,9 @@
       <c r="E169" t="s">
         <v>1171</v>
       </c>
+      <c r="F169" t="s">
+        <v>1454</v>
+      </c>
       <c r="G169" t="s">
         <v>990</v>
       </c>
@@ -12082,8 +12592,8 @@
       </c>
     </row>
     <row r="170" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A170">
-        <v>83</v>
+      <c r="A170" t="s">
+        <v>1455</v>
       </c>
       <c r="B170" t="s">
         <v>712</v>
@@ -12097,6 +12607,9 @@
       <c r="E170" t="s">
         <v>1174</v>
       </c>
+      <c r="F170" t="s">
+        <v>1454</v>
+      </c>
       <c r="G170" t="s">
         <v>994</v>
       </c>
@@ -12114,8 +12627,8 @@
       </c>
     </row>
     <row r="171" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A171">
-        <v>82</v>
+      <c r="A171" t="s">
+        <v>1455</v>
       </c>
       <c r="B171" t="s">
         <v>703</v>
@@ -12129,6 +12642,9 @@
       <c r="E171" t="s">
         <v>1177</v>
       </c>
+      <c r="F171" t="s">
+        <v>1454</v>
+      </c>
       <c r="G171" t="s">
         <v>981</v>
       </c>
@@ -12146,8 +12662,8 @@
       </c>
     </row>
     <row r="172" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A172">
-        <v>84</v>
+      <c r="A172" t="s">
+        <v>1455</v>
       </c>
       <c r="B172" t="s">
         <v>712</v>
@@ -12161,6 +12677,9 @@
       <c r="E172" t="s">
         <v>1180</v>
       </c>
+      <c r="F172" t="s">
+        <v>1454</v>
+      </c>
       <c r="G172" t="s">
         <v>980</v>
       </c>
@@ -12178,8 +12697,8 @@
       </c>
     </row>
     <row r="173" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A173">
-        <v>83</v>
+      <c r="A173" t="s">
+        <v>1455</v>
       </c>
       <c r="B173" t="s">
         <v>703</v>
@@ -12193,6 +12712,9 @@
       <c r="E173" t="s">
         <v>1182</v>
       </c>
+      <c r="F173" t="s">
+        <v>1454</v>
+      </c>
       <c r="G173" t="s">
         <v>990</v>
       </c>
@@ -12210,8 +12732,8 @@
       </c>
     </row>
     <row r="174" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A174">
-        <v>85</v>
+      <c r="A174" t="s">
+        <v>1455</v>
       </c>
       <c r="B174" t="s">
         <v>712</v>
@@ -12225,6 +12747,9 @@
       <c r="E174" t="s">
         <v>1185</v>
       </c>
+      <c r="F174" t="s">
+        <v>1454</v>
+      </c>
       <c r="G174" t="s">
         <v>980</v>
       </c>
@@ -12239,8 +12764,8 @@
       </c>
     </row>
     <row r="175" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A175">
-        <v>84</v>
+      <c r="A175" t="s">
+        <v>1455</v>
       </c>
       <c r="B175" t="s">
         <v>703</v>
@@ -12254,6 +12779,9 @@
       <c r="E175" t="s">
         <v>1188</v>
       </c>
+      <c r="F175" t="s">
+        <v>1454</v>
+      </c>
       <c r="G175" t="s">
         <v>981</v>
       </c>
@@ -12268,8 +12796,8 @@
       </c>
     </row>
     <row r="176" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A176">
-        <v>86</v>
+      <c r="A176" t="s">
+        <v>1455</v>
       </c>
       <c r="B176" t="s">
         <v>712</v>
@@ -12283,6 +12811,9 @@
       <c r="E176" t="s">
         <v>1191</v>
       </c>
+      <c r="F176" t="s">
+        <v>1454</v>
+      </c>
       <c r="G176" t="s">
         <v>994</v>
       </c>
@@ -12300,8 +12831,8 @@
       </c>
     </row>
     <row r="177" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A177">
-        <v>85</v>
+      <c r="A177" t="s">
+        <v>1455</v>
       </c>
       <c r="B177" t="s">
         <v>703</v>
@@ -12315,6 +12846,9 @@
       <c r="E177" t="s">
         <v>1194</v>
       </c>
+      <c r="F177" t="s">
+        <v>1454</v>
+      </c>
       <c r="G177" t="s">
         <v>981</v>
       </c>
@@ -12332,8 +12866,8 @@
       </c>
     </row>
     <row r="178" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A178">
-        <v>87</v>
+      <c r="A178" t="s">
+        <v>1455</v>
       </c>
       <c r="B178" t="s">
         <v>712</v>
@@ -12347,6 +12881,9 @@
       <c r="E178" t="s">
         <v>1197</v>
       </c>
+      <c r="F178" t="s">
+        <v>1454</v>
+      </c>
       <c r="G178" t="s">
         <v>994</v>
       </c>
@@ -12364,8 +12901,8 @@
       </c>
     </row>
     <row r="179" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A179">
-        <v>86</v>
+      <c r="A179" t="s">
+        <v>1455</v>
       </c>
       <c r="B179" t="s">
         <v>703</v>
@@ -12379,6 +12916,9 @@
       <c r="E179" t="s">
         <v>1198</v>
       </c>
+      <c r="F179" t="s">
+        <v>1454</v>
+      </c>
       <c r="G179" t="s">
         <v>981</v>
       </c>
@@ -12396,8 +12936,8 @@
       </c>
     </row>
     <row r="180" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A180">
-        <v>88</v>
+      <c r="A180" t="s">
+        <v>1455</v>
       </c>
       <c r="B180" t="s">
         <v>712</v>
@@ -12411,6 +12951,9 @@
       <c r="E180" t="s">
         <v>1200</v>
       </c>
+      <c r="F180" t="s">
+        <v>1454</v>
+      </c>
       <c r="G180" t="s">
         <v>711</v>
       </c>
@@ -12428,8 +12971,8 @@
       </c>
     </row>
     <row r="181" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A181">
-        <v>87</v>
+      <c r="A181" t="s">
+        <v>1455</v>
       </c>
       <c r="B181" t="s">
         <v>703</v>
@@ -12443,6 +12986,9 @@
       <c r="E181" t="s">
         <v>1202</v>
       </c>
+      <c r="F181" t="s">
+        <v>1454</v>
+      </c>
       <c r="G181" t="s">
         <v>981</v>
       </c>
@@ -12460,8 +13006,8 @@
       </c>
     </row>
     <row r="182" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A182">
-        <v>89</v>
+      <c r="A182" t="s">
+        <v>1455</v>
       </c>
       <c r="B182" t="s">
         <v>712</v>
@@ -12475,6 +13021,9 @@
       <c r="E182" t="s">
         <v>1205</v>
       </c>
+      <c r="F182" t="s">
+        <v>1454</v>
+      </c>
       <c r="G182" t="s">
         <v>994</v>
       </c>
@@ -12492,8 +13041,8 @@
       </c>
     </row>
     <row r="183" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A183">
-        <v>88</v>
+      <c r="A183" t="s">
+        <v>1455</v>
       </c>
       <c r="B183" t="s">
         <v>703</v>
@@ -12507,6 +13056,9 @@
       <c r="E183" t="s">
         <v>1208</v>
       </c>
+      <c r="F183" t="s">
+        <v>1454</v>
+      </c>
       <c r="G183" t="s">
         <v>981</v>
       </c>
@@ -12524,8 +13076,8 @@
       </c>
     </row>
     <row r="184" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A184">
-        <v>90</v>
+      <c r="A184" t="s">
+        <v>1455</v>
       </c>
       <c r="B184" t="s">
         <v>712</v>
@@ -12539,6 +13091,9 @@
       <c r="E184" t="s">
         <v>1211</v>
       </c>
+      <c r="F184" t="s">
+        <v>1454</v>
+      </c>
       <c r="G184" t="s">
         <v>980</v>
       </c>
@@ -12556,8 +13111,8 @@
       </c>
     </row>
     <row r="185" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A185">
-        <v>89</v>
+      <c r="A185" t="s">
+        <v>1455</v>
       </c>
       <c r="B185" t="s">
         <v>703</v>
@@ -12571,6 +13126,9 @@
       <c r="E185" t="s">
         <v>1214</v>
       </c>
+      <c r="F185" t="s">
+        <v>1454</v>
+      </c>
       <c r="G185" t="s">
         <v>981</v>
       </c>
@@ -12588,8 +13146,8 @@
       </c>
     </row>
     <row r="186" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A186">
-        <v>91</v>
+      <c r="A186" t="s">
+        <v>1455</v>
       </c>
       <c r="B186" t="s">
         <v>712</v>
@@ -12603,10 +13161,13 @@
       <c r="E186" t="s">
         <v>1217</v>
       </c>
+      <c r="F186" t="s">
+        <v>1454</v>
+      </c>
     </row>
     <row r="187" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A187">
-        <v>90</v>
+      <c r="A187" t="s">
+        <v>1455</v>
       </c>
       <c r="B187" t="s">
         <v>703</v>
@@ -12620,6 +13181,9 @@
       <c r="E187" t="s">
         <v>1220</v>
       </c>
+      <c r="F187" t="s">
+        <v>1454</v>
+      </c>
       <c r="G187" t="s">
         <v>990</v>
       </c>
@@ -12637,8 +13201,8 @@
       </c>
     </row>
     <row r="188" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A188">
-        <v>92</v>
+      <c r="A188" t="s">
+        <v>1455</v>
       </c>
       <c r="B188" t="s">
         <v>712</v>
@@ -12652,6 +13216,9 @@
       <c r="E188" t="s">
         <v>1222</v>
       </c>
+      <c r="F188" t="s">
+        <v>1454</v>
+      </c>
       <c r="G188" t="s">
         <v>980</v>
       </c>
@@ -12669,8 +13236,8 @@
       </c>
     </row>
     <row r="189" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A189">
-        <v>91</v>
+      <c r="A189" t="s">
+        <v>1455</v>
       </c>
       <c r="B189" t="s">
         <v>703</v>
@@ -12684,6 +13251,9 @@
       <c r="E189" t="s">
         <v>1224</v>
       </c>
+      <c r="F189" t="s">
+        <v>1454</v>
+      </c>
       <c r="G189" t="s">
         <v>981</v>
       </c>
@@ -12701,8 +13271,8 @@
       </c>
     </row>
     <row r="190" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A190">
-        <v>93</v>
+      <c r="A190" t="s">
+        <v>1455</v>
       </c>
       <c r="B190" t="s">
         <v>712</v>
@@ -12716,6 +13286,9 @@
       <c r="E190" t="s">
         <v>1227</v>
       </c>
+      <c r="F190" t="s">
+        <v>1454</v>
+      </c>
       <c r="G190" t="s">
         <v>711</v>
       </c>
@@ -12733,8 +13306,8 @@
       </c>
     </row>
     <row r="191" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A191">
-        <v>92</v>
+      <c r="A191" t="s">
+        <v>1455</v>
       </c>
       <c r="B191" t="s">
         <v>703</v>
@@ -12748,6 +13321,9 @@
       <c r="E191" t="s">
         <v>1228</v>
       </c>
+      <c r="F191" t="s">
+        <v>1454</v>
+      </c>
       <c r="G191" t="s">
         <v>981</v>
       </c>
@@ -12765,8 +13341,8 @@
       </c>
     </row>
     <row r="192" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A192">
-        <v>94</v>
+      <c r="A192" t="s">
+        <v>1455</v>
       </c>
       <c r="B192" t="s">
         <v>712</v>
@@ -12780,6 +13356,9 @@
       <c r="E192" t="s">
         <v>1231</v>
       </c>
+      <c r="F192" t="s">
+        <v>1454</v>
+      </c>
       <c r="G192" t="s">
         <v>994</v>
       </c>
@@ -12797,8 +13376,8 @@
       </c>
     </row>
     <row r="193" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A193">
-        <v>93</v>
+      <c r="A193" t="s">
+        <v>1455</v>
       </c>
       <c r="B193" t="s">
         <v>703</v>
@@ -12812,6 +13391,9 @@
       <c r="E193" t="s">
         <v>1232</v>
       </c>
+      <c r="F193" t="s">
+        <v>1454</v>
+      </c>
       <c r="G193" t="s">
         <v>990</v>
       </c>
@@ -12829,8 +13411,8 @@
       </c>
     </row>
     <row r="194" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A194">
-        <v>95</v>
+      <c r="A194" t="s">
+        <v>1455</v>
       </c>
       <c r="B194" t="s">
         <v>712</v>
@@ -12844,6 +13426,9 @@
       <c r="E194" t="s">
         <v>1235</v>
       </c>
+      <c r="F194" t="s">
+        <v>1454</v>
+      </c>
       <c r="G194" t="s">
         <v>980</v>
       </c>
@@ -12861,8 +13446,8 @@
       </c>
     </row>
     <row r="195" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A195">
-        <v>2</v>
+      <c r="A195" t="s">
+        <v>1455</v>
       </c>
       <c r="B195" t="s">
         <v>973</v>
@@ -12876,10 +13461,13 @@
       <c r="E195" t="s">
         <v>1236</v>
       </c>
+      <c r="F195" t="s">
+        <v>1454</v>
+      </c>
     </row>
     <row r="196" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A196">
-        <v>1</v>
+      <c r="A196" t="s">
+        <v>1455</v>
       </c>
       <c r="B196" t="s">
         <v>1237</v>
@@ -12893,10 +13481,13 @@
       <c r="E196" t="s">
         <v>1238</v>
       </c>
+      <c r="F196" t="s">
+        <v>1454</v>
+      </c>
     </row>
     <row r="197" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A197">
-        <v>3</v>
+      <c r="A197" t="s">
+        <v>1455</v>
       </c>
       <c r="B197" t="s">
         <v>702</v>
@@ -12910,10 +13501,13 @@
       <c r="E197" t="s">
         <v>1238</v>
       </c>
+      <c r="F197" t="s">
+        <v>1454</v>
+      </c>
     </row>
     <row r="198" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A198">
-        <v>94</v>
+      <c r="A198" t="s">
+        <v>1455</v>
       </c>
       <c r="B198" t="s">
         <v>703</v>
@@ -12927,6 +13521,9 @@
       <c r="E198" t="s">
         <v>1241</v>
       </c>
+      <c r="F198" t="s">
+        <v>1454</v>
+      </c>
       <c r="G198" t="s">
         <v>723</v>
       </c>
@@ -12944,8 +13541,8 @@
       </c>
     </row>
     <row r="199" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A199">
-        <v>96</v>
+      <c r="A199" t="s">
+        <v>1455</v>
       </c>
       <c r="B199" t="s">
         <v>712</v>
@@ -12959,6 +13556,9 @@
       <c r="E199" t="s">
         <v>1244</v>
       </c>
+      <c r="F199" t="s">
+        <v>1454</v>
+      </c>
       <c r="G199" t="s">
         <v>994</v>
       </c>
@@ -12976,8 +13576,8 @@
       </c>
     </row>
     <row r="200" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A200">
-        <v>95</v>
+      <c r="A200" t="s">
+        <v>1455</v>
       </c>
       <c r="B200" t="s">
         <v>703</v>
@@ -12991,6 +13591,9 @@
       <c r="E200" t="s">
         <v>1247</v>
       </c>
+      <c r="F200" t="s">
+        <v>1454</v>
+      </c>
       <c r="G200" t="s">
         <v>723</v>
       </c>
@@ -13008,8 +13611,8 @@
       </c>
     </row>
     <row r="201" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A201">
-        <v>97</v>
+      <c r="A201" t="s">
+        <v>1455</v>
       </c>
       <c r="B201" t="s">
         <v>712</v>
@@ -13023,6 +13626,9 @@
       <c r="E201" t="s">
         <v>1249</v>
       </c>
+      <c r="F201" t="s">
+        <v>1454</v>
+      </c>
       <c r="G201" t="s">
         <v>980</v>
       </c>
@@ -13040,8 +13646,8 @@
       </c>
     </row>
     <row r="202" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A202">
-        <v>96</v>
+      <c r="A202" t="s">
+        <v>1455</v>
       </c>
       <c r="B202" t="s">
         <v>703</v>
@@ -13055,6 +13661,9 @@
       <c r="E202" t="s">
         <v>1252</v>
       </c>
+      <c r="F202" t="s">
+        <v>1454</v>
+      </c>
       <c r="G202" t="s">
         <v>719</v>
       </c>
@@ -13072,8 +13681,8 @@
       </c>
     </row>
     <row r="203" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A203">
-        <v>98</v>
+      <c r="A203" t="s">
+        <v>1455</v>
       </c>
       <c r="B203" t="s">
         <v>712</v>
@@ -13087,6 +13696,9 @@
       <c r="E203" t="s">
         <v>1254</v>
       </c>
+      <c r="F203" t="s">
+        <v>1454</v>
+      </c>
       <c r="G203" t="s">
         <v>994</v>
       </c>
@@ -13104,8 +13716,8 @@
       </c>
     </row>
     <row r="204" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A204">
-        <v>97</v>
+      <c r="A204" t="s">
+        <v>1455</v>
       </c>
       <c r="B204" t="s">
         <v>703</v>
@@ -13119,6 +13731,9 @@
       <c r="E204" t="s">
         <v>1256</v>
       </c>
+      <c r="F204" t="s">
+        <v>1454</v>
+      </c>
       <c r="G204" t="s">
         <v>723</v>
       </c>
@@ -13133,8 +13748,8 @@
       </c>
     </row>
     <row r="205" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A205">
-        <v>99</v>
+      <c r="A205" t="s">
+        <v>1455</v>
       </c>
       <c r="B205" t="s">
         <v>712</v>
@@ -13148,6 +13763,9 @@
       <c r="E205" t="s">
         <v>1259</v>
       </c>
+      <c r="F205" t="s">
+        <v>1454</v>
+      </c>
       <c r="G205" t="s">
         <v>980</v>
       </c>
@@ -13165,8 +13783,8 @@
       </c>
     </row>
     <row r="206" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A206">
-        <v>98</v>
+      <c r="A206" t="s">
+        <v>1455</v>
       </c>
       <c r="B206" t="s">
         <v>703</v>
@@ -13180,6 +13798,9 @@
       <c r="E206" t="s">
         <v>1261</v>
       </c>
+      <c r="F206" t="s">
+        <v>1454</v>
+      </c>
       <c r="G206" t="s">
         <v>707</v>
       </c>
@@ -13197,8 +13818,8 @@
       </c>
     </row>
     <row r="207" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A207">
-        <v>100</v>
+      <c r="A207" t="s">
+        <v>1455</v>
       </c>
       <c r="B207" t="s">
         <v>712</v>
@@ -13212,6 +13833,9 @@
       <c r="E207" t="s">
         <v>1263</v>
       </c>
+      <c r="F207" t="s">
+        <v>1454</v>
+      </c>
       <c r="G207" t="s">
         <v>994</v>
       </c>
@@ -13229,8 +13853,8 @@
       </c>
     </row>
     <row r="208" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A208">
-        <v>99</v>
+      <c r="A208" t="s">
+        <v>1455</v>
       </c>
       <c r="B208" t="s">
         <v>703</v>
@@ -13244,6 +13868,9 @@
       <c r="E208" t="s">
         <v>1265</v>
       </c>
+      <c r="F208" t="s">
+        <v>1454</v>
+      </c>
       <c r="G208" t="s">
         <v>719</v>
       </c>
@@ -13261,8 +13888,8 @@
       </c>
     </row>
     <row r="209" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A209">
-        <v>101</v>
+      <c r="A209" t="s">
+        <v>1455</v>
       </c>
       <c r="B209" t="s">
         <v>712</v>
@@ -13276,6 +13903,9 @@
       <c r="E209" t="s">
         <v>1268</v>
       </c>
+      <c r="F209" t="s">
+        <v>1454</v>
+      </c>
       <c r="G209" t="s">
         <v>980</v>
       </c>
@@ -13293,8 +13923,8 @@
       </c>
     </row>
     <row r="210" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A210">
-        <v>100</v>
+      <c r="A210" t="s">
+        <v>1455</v>
       </c>
       <c r="B210" t="s">
         <v>703</v>
@@ -13308,6 +13938,9 @@
       <c r="E210" t="s">
         <v>1270</v>
       </c>
+      <c r="F210" t="s">
+        <v>1454</v>
+      </c>
       <c r="G210" t="s">
         <v>719</v>
       </c>
@@ -13325,8 +13958,8 @@
       </c>
     </row>
     <row r="211" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A211">
-        <v>102</v>
+      <c r="A211" t="s">
+        <v>1455</v>
       </c>
       <c r="B211" t="s">
         <v>712</v>
@@ -13340,6 +13973,9 @@
       <c r="E211" t="s">
         <v>1272</v>
       </c>
+      <c r="F211" t="s">
+        <v>1454</v>
+      </c>
       <c r="G211" t="s">
         <v>716</v>
       </c>
@@ -13357,8 +13993,8 @@
       </c>
     </row>
     <row r="212" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A212">
-        <v>101</v>
+      <c r="A212" t="s">
+        <v>1455</v>
       </c>
       <c r="B212" t="s">
         <v>703</v>
@@ -13372,6 +14008,9 @@
       <c r="E212" t="s">
         <v>1273</v>
       </c>
+      <c r="F212" t="s">
+        <v>1454</v>
+      </c>
       <c r="G212" t="s">
         <v>723</v>
       </c>
@@ -13389,8 +14028,8 @@
       </c>
     </row>
     <row r="213" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A213">
-        <v>103</v>
+      <c r="A213" t="s">
+        <v>1455</v>
       </c>
       <c r="B213" t="s">
         <v>712</v>
@@ -13404,6 +14043,9 @@
       <c r="E213" t="s">
         <v>1276</v>
       </c>
+      <c r="F213" t="s">
+        <v>1454</v>
+      </c>
       <c r="G213" t="s">
         <v>716</v>
       </c>
@@ -13421,8 +14063,8 @@
       </c>
     </row>
     <row r="214" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A214">
-        <v>102</v>
+      <c r="A214" t="s">
+        <v>1455</v>
       </c>
       <c r="B214" t="s">
         <v>703</v>
@@ -13436,6 +14078,9 @@
       <c r="E214" t="s">
         <v>1278</v>
       </c>
+      <c r="F214" t="s">
+        <v>1454</v>
+      </c>
       <c r="G214" t="s">
         <v>723</v>
       </c>
@@ -13453,8 +14098,8 @@
       </c>
     </row>
     <row r="215" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A215">
-        <v>104</v>
+      <c r="A215" t="s">
+        <v>1455</v>
       </c>
       <c r="B215" t="s">
         <v>712</v>
@@ -13468,6 +14113,9 @@
       <c r="E215" t="s">
         <v>1281</v>
       </c>
+      <c r="F215" t="s">
+        <v>1454</v>
+      </c>
       <c r="G215" t="s">
         <v>716</v>
       </c>
@@ -13485,8 +14133,8 @@
       </c>
     </row>
     <row r="216" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A216">
-        <v>103</v>
+      <c r="A216" t="s">
+        <v>1455</v>
       </c>
       <c r="B216" t="s">
         <v>703</v>
@@ -13500,6 +14148,9 @@
       <c r="E216" t="s">
         <v>1284</v>
       </c>
+      <c r="F216" t="s">
+        <v>1454</v>
+      </c>
       <c r="G216" t="s">
         <v>723</v>
       </c>
@@ -13514,8 +14165,8 @@
       </c>
     </row>
     <row r="217" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A217">
-        <v>105</v>
+      <c r="A217" t="s">
+        <v>1455</v>
       </c>
       <c r="B217" t="s">
         <v>712</v>
@@ -13529,6 +14180,9 @@
       <c r="E217" t="s">
         <v>1287</v>
       </c>
+      <c r="F217" t="s">
+        <v>1454</v>
+      </c>
       <c r="G217" t="s">
         <v>980</v>
       </c>
@@ -13546,8 +14200,8 @@
       </c>
     </row>
     <row r="218" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A218">
-        <v>104</v>
+      <c r="A218" t="s">
+        <v>1455</v>
       </c>
       <c r="B218" t="s">
         <v>703</v>
@@ -13561,6 +14215,9 @@
       <c r="E218" t="s">
         <v>1290</v>
       </c>
+      <c r="F218" t="s">
+        <v>1454</v>
+      </c>
       <c r="G218" t="s">
         <v>707</v>
       </c>
@@ -13578,8 +14235,8 @@
       </c>
     </row>
     <row r="219" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A219">
-        <v>106</v>
+      <c r="A219" t="s">
+        <v>1455</v>
       </c>
       <c r="B219" t="s">
         <v>712</v>
@@ -13593,6 +14250,9 @@
       <c r="E219" t="s">
         <v>1293</v>
       </c>
+      <c r="F219" t="s">
+        <v>1454</v>
+      </c>
       <c r="G219" t="s">
         <v>716</v>
       </c>
@@ -13610,8 +14270,8 @@
       </c>
     </row>
     <row r="220" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A220">
-        <v>105</v>
+      <c r="A220" t="s">
+        <v>1455</v>
       </c>
       <c r="B220" t="s">
         <v>703</v>
@@ -13625,6 +14285,9 @@
       <c r="E220" t="s">
         <v>1296</v>
       </c>
+      <c r="F220" t="s">
+        <v>1454</v>
+      </c>
       <c r="G220" t="s">
         <v>723</v>
       </c>
@@ -13639,8 +14302,8 @@
       </c>
     </row>
     <row r="221" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A221">
-        <v>107</v>
+      <c r="A221" t="s">
+        <v>1455</v>
       </c>
       <c r="B221" t="s">
         <v>712</v>
@@ -13654,6 +14317,9 @@
       <c r="E221" t="s">
         <v>1299</v>
       </c>
+      <c r="F221" t="s">
+        <v>1454</v>
+      </c>
       <c r="G221" t="s">
         <v>980</v>
       </c>
@@ -13665,8 +14331,8 @@
       </c>
     </row>
     <row r="222" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A222">
-        <v>1</v>
+      <c r="A222" t="s">
+        <v>1455</v>
       </c>
       <c r="B222" t="s">
         <v>1301</v>
@@ -13680,6 +14346,9 @@
       <c r="E222" t="s">
         <v>1304</v>
       </c>
+      <c r="F222" t="s">
+        <v>1454</v>
+      </c>
       <c r="G222" t="s">
         <v>707</v>
       </c>
@@ -13697,8 +14366,8 @@
       </c>
     </row>
     <row r="223" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A223">
-        <v>108</v>
+      <c r="A223" t="s">
+        <v>1455</v>
       </c>
       <c r="B223" t="s">
         <v>712</v>
@@ -13712,6 +14381,9 @@
       <c r="E223" t="s">
         <v>1307</v>
       </c>
+      <c r="F223" t="s">
+        <v>1454</v>
+      </c>
       <c r="G223" t="s">
         <v>980</v>
       </c>
@@ -13729,8 +14401,8 @@
       </c>
     </row>
     <row r="224" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A224">
-        <v>106</v>
+      <c r="A224" t="s">
+        <v>1455</v>
       </c>
       <c r="B224" t="s">
         <v>703</v>
@@ -13744,6 +14416,9 @@
       <c r="E224" t="s">
         <v>1309</v>
       </c>
+      <c r="F224" t="s">
+        <v>1454</v>
+      </c>
       <c r="G224" t="s">
         <v>707</v>
       </c>
@@ -13761,8 +14436,8 @@
       </c>
     </row>
     <row r="225" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A225">
-        <v>109</v>
+      <c r="A225" t="s">
+        <v>1455</v>
       </c>
       <c r="B225" t="s">
         <v>712</v>
@@ -13776,6 +14451,9 @@
       <c r="E225" t="s">
         <v>1312</v>
       </c>
+      <c r="F225" t="s">
+        <v>1454</v>
+      </c>
       <c r="G225" t="s">
         <v>716</v>
       </c>
@@ -13793,8 +14471,8 @@
       </c>
     </row>
     <row r="226" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A226">
-        <v>107</v>
+      <c r="A226" t="s">
+        <v>1455</v>
       </c>
       <c r="B226" t="s">
         <v>703</v>
@@ -13808,6 +14486,9 @@
       <c r="E226" t="s">
         <v>1315</v>
       </c>
+      <c r="F226" t="s">
+        <v>1454</v>
+      </c>
       <c r="G226" t="s">
         <v>723</v>
       </c>
@@ -13825,8 +14506,8 @@
       </c>
     </row>
     <row r="227" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A227">
-        <v>110</v>
+      <c r="A227" t="s">
+        <v>1455</v>
       </c>
       <c r="B227" t="s">
         <v>712</v>
@@ -13840,6 +14521,9 @@
       <c r="E227" t="s">
         <v>1318</v>
       </c>
+      <c r="F227" t="s">
+        <v>1454</v>
+      </c>
       <c r="G227" t="s">
         <v>980</v>
       </c>
@@ -13857,8 +14541,8 @@
       </c>
     </row>
     <row r="228" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A228">
-        <v>108</v>
+      <c r="A228" t="s">
+        <v>1455</v>
       </c>
       <c r="B228" t="s">
         <v>703</v>
@@ -13872,6 +14556,9 @@
       <c r="E228" t="s">
         <v>1319</v>
       </c>
+      <c r="F228" t="s">
+        <v>1454</v>
+      </c>
       <c r="G228" t="s">
         <v>723</v>
       </c>
@@ -13886,8 +14573,8 @@
       </c>
     </row>
     <row r="229" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A229">
-        <v>111</v>
+      <c r="A229" t="s">
+        <v>1455</v>
       </c>
       <c r="B229" t="s">
         <v>712</v>
@@ -13901,6 +14588,9 @@
       <c r="E229" t="s">
         <v>1322</v>
       </c>
+      <c r="F229" t="s">
+        <v>1454</v>
+      </c>
       <c r="G229" t="s">
         <v>716</v>
       </c>
@@ -13918,8 +14608,8 @@
       </c>
     </row>
     <row r="230" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A230">
-        <v>109</v>
+      <c r="A230" t="s">
+        <v>1455</v>
       </c>
       <c r="B230" t="s">
         <v>703</v>
@@ -13933,10 +14623,13 @@
       <c r="E230" t="s">
         <v>1325</v>
       </c>
+      <c r="F230" t="s">
+        <v>1454</v>
+      </c>
     </row>
     <row r="231" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A231">
-        <v>112</v>
+      <c r="A231" t="s">
+        <v>1455</v>
       </c>
       <c r="B231" t="s">
         <v>712</v>
@@ -13950,6 +14643,9 @@
       <c r="E231" t="s">
         <v>1328</v>
       </c>
+      <c r="F231" t="s">
+        <v>1454</v>
+      </c>
       <c r="G231" t="s">
         <v>716</v>
       </c>
@@ -13964,8 +14660,8 @@
       </c>
     </row>
     <row r="232" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A232">
-        <v>110</v>
+      <c r="A232" t="s">
+        <v>1455</v>
       </c>
       <c r="B232" t="s">
         <v>703</v>
@@ -13979,6 +14675,9 @@
       <c r="E232" t="s">
         <v>1329</v>
       </c>
+      <c r="F232" t="s">
+        <v>1454</v>
+      </c>
       <c r="G232" t="s">
         <v>723</v>
       </c>
@@ -13996,8 +14695,8 @@
       </c>
     </row>
     <row r="233" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A233">
-        <v>113</v>
+      <c r="A233" t="s">
+        <v>1455</v>
       </c>
       <c r="B233" t="s">
         <v>712</v>
@@ -14011,6 +14710,9 @@
       <c r="E233" t="s">
         <v>1331</v>
       </c>
+      <c r="F233" t="s">
+        <v>1454</v>
+      </c>
       <c r="G233" t="s">
         <v>980</v>
       </c>
@@ -14028,8 +14730,8 @@
       </c>
     </row>
     <row r="234" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A234">
-        <v>111</v>
+      <c r="A234" t="s">
+        <v>1455</v>
       </c>
       <c r="B234" t="s">
         <v>703</v>
@@ -14043,6 +14745,9 @@
       <c r="E234" t="s">
         <v>1333</v>
       </c>
+      <c r="F234" t="s">
+        <v>1454</v>
+      </c>
       <c r="G234" t="s">
         <v>707</v>
       </c>
@@ -14057,8 +14762,8 @@
       </c>
     </row>
     <row r="235" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A235">
-        <v>114</v>
+      <c r="A235" t="s">
+        <v>1455</v>
       </c>
       <c r="B235" t="s">
         <v>712</v>
@@ -14072,6 +14777,9 @@
       <c r="E235" t="s">
         <v>1335</v>
       </c>
+      <c r="F235" t="s">
+        <v>1454</v>
+      </c>
       <c r="G235" t="s">
         <v>716</v>
       </c>
@@ -14089,8 +14797,8 @@
       </c>
     </row>
     <row r="236" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A236">
-        <v>112</v>
+      <c r="A236" t="s">
+        <v>1455</v>
       </c>
       <c r="B236" t="s">
         <v>703</v>
@@ -14104,6 +14812,9 @@
       <c r="E236" t="s">
         <v>1337</v>
       </c>
+      <c r="F236" t="s">
+        <v>1454</v>
+      </c>
       <c r="G236" t="s">
         <v>990</v>
       </c>
@@ -14121,8 +14832,8 @@
       </c>
     </row>
     <row r="237" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A237">
-        <v>115</v>
+      <c r="A237" t="s">
+        <v>1455</v>
       </c>
       <c r="B237" t="s">
         <v>712</v>
@@ -14136,6 +14847,9 @@
       <c r="E237" t="s">
         <v>1340</v>
       </c>
+      <c r="F237" t="s">
+        <v>1454</v>
+      </c>
       <c r="G237" t="s">
         <v>716</v>
       </c>
@@ -14153,8 +14867,8 @@
       </c>
     </row>
     <row r="238" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A238">
-        <v>113</v>
+      <c r="A238" t="s">
+        <v>1455</v>
       </c>
       <c r="B238" t="s">
         <v>703</v>
@@ -14168,6 +14882,9 @@
       <c r="E238" t="s">
         <v>1343</v>
       </c>
+      <c r="F238" t="s">
+        <v>1454</v>
+      </c>
       <c r="G238" t="s">
         <v>997</v>
       </c>
@@ -14185,8 +14902,8 @@
       </c>
     </row>
     <row r="239" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A239">
-        <v>116</v>
+      <c r="A239" t="s">
+        <v>1455</v>
       </c>
       <c r="B239" t="s">
         <v>712</v>
@@ -14200,6 +14917,9 @@
       <c r="E239" t="s">
         <v>1345</v>
       </c>
+      <c r="F239" t="s">
+        <v>1454</v>
+      </c>
       <c r="G239" t="s">
         <v>980</v>
       </c>
@@ -14217,8 +14937,8 @@
       </c>
     </row>
     <row r="240" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A240">
-        <v>114</v>
+      <c r="A240" t="s">
+        <v>1455</v>
       </c>
       <c r="B240" t="s">
         <v>703</v>
@@ -14232,6 +14952,9 @@
       <c r="E240" t="s">
         <v>1347</v>
       </c>
+      <c r="F240" t="s">
+        <v>1454</v>
+      </c>
       <c r="G240" t="s">
         <v>990</v>
       </c>
@@ -14249,8 +14972,8 @@
       </c>
     </row>
     <row r="241" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A241">
-        <v>117</v>
+      <c r="A241" t="s">
+        <v>1455</v>
       </c>
       <c r="B241" t="s">
         <v>712</v>
@@ -14264,6 +14987,9 @@
       <c r="E241" t="s">
         <v>1349</v>
       </c>
+      <c r="F241" t="s">
+        <v>1454</v>
+      </c>
       <c r="G241" t="s">
         <v>716</v>
       </c>
@@ -14281,8 +15007,8 @@
       </c>
     </row>
     <row r="242" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A242">
-        <v>115</v>
+      <c r="A242" t="s">
+        <v>1455</v>
       </c>
       <c r="B242" t="s">
         <v>703</v>
@@ -14296,6 +15022,9 @@
       <c r="E242" t="s">
         <v>1352</v>
       </c>
+      <c r="F242" t="s">
+        <v>1454</v>
+      </c>
       <c r="G242" t="s">
         <v>997</v>
       </c>
@@ -14313,8 +15042,8 @@
       </c>
     </row>
     <row r="243" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A243">
-        <v>118</v>
+      <c r="A243" t="s">
+        <v>1455</v>
       </c>
       <c r="B243" t="s">
         <v>712</v>
@@ -14328,6 +15057,9 @@
       <c r="E243" t="s">
         <v>1355</v>
       </c>
+      <c r="F243" t="s">
+        <v>1454</v>
+      </c>
       <c r="G243" t="s">
         <v>980</v>
       </c>
@@ -14345,8 +15077,8 @@
       </c>
     </row>
     <row r="244" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A244">
-        <v>116</v>
+      <c r="A244" t="s">
+        <v>1455</v>
       </c>
       <c r="B244" t="s">
         <v>703</v>
@@ -14360,6 +15092,9 @@
       <c r="E244" t="s">
         <v>1357</v>
       </c>
+      <c r="F244" t="s">
+        <v>1454</v>
+      </c>
       <c r="G244" t="s">
         <v>990</v>
       </c>
@@ -14377,8 +15112,8 @@
       </c>
     </row>
     <row r="245" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A245">
-        <v>119</v>
+      <c r="A245" t="s">
+        <v>1455</v>
       </c>
       <c r="B245" t="s">
         <v>712</v>
@@ -14392,6 +15127,9 @@
       <c r="E245" t="s">
         <v>1360</v>
       </c>
+      <c r="F245" t="s">
+        <v>1454</v>
+      </c>
       <c r="G245" t="s">
         <v>716</v>
       </c>
@@ -14409,8 +15147,8 @@
       </c>
     </row>
     <row r="246" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A246">
-        <v>117</v>
+      <c r="A246" t="s">
+        <v>1455</v>
       </c>
       <c r="B246" t="s">
         <v>703</v>
@@ -14424,6 +15162,9 @@
       <c r="E246" t="s">
         <v>1363</v>
       </c>
+      <c r="F246" t="s">
+        <v>1454</v>
+      </c>
       <c r="G246" t="s">
         <v>990</v>
       </c>
@@ -14441,8 +15182,8 @@
       </c>
     </row>
     <row r="247" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A247">
-        <v>120</v>
+      <c r="A247" t="s">
+        <v>1455</v>
       </c>
       <c r="B247" t="s">
         <v>712</v>
@@ -14456,6 +15197,9 @@
       <c r="E247" t="s">
         <v>1364</v>
       </c>
+      <c r="F247" t="s">
+        <v>1454</v>
+      </c>
       <c r="G247" t="s">
         <v>716</v>
       </c>
@@ -14473,8 +15217,8 @@
       </c>
     </row>
     <row r="248" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A248">
-        <v>118</v>
+      <c r="A248" t="s">
+        <v>1455</v>
       </c>
       <c r="B248" t="s">
         <v>703</v>
@@ -14488,6 +15232,9 @@
       <c r="E248" t="s">
         <v>1366</v>
       </c>
+      <c r="F248" t="s">
+        <v>1454</v>
+      </c>
       <c r="G248" t="s">
         <v>997</v>
       </c>
@@ -14505,8 +15252,8 @@
       </c>
     </row>
     <row r="249" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A249">
-        <v>121</v>
+      <c r="A249" t="s">
+        <v>1455</v>
       </c>
       <c r="B249" t="s">
         <v>712</v>
@@ -14520,6 +15267,9 @@
       <c r="E249" t="s">
         <v>1368</v>
       </c>
+      <c r="F249" t="s">
+        <v>1454</v>
+      </c>
       <c r="G249" t="s">
         <v>980</v>
       </c>
@@ -14537,8 +15287,8 @@
       </c>
     </row>
     <row r="250" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A250">
-        <v>119</v>
+      <c r="A250" t="s">
+        <v>1455</v>
       </c>
       <c r="B250" t="s">
         <v>703</v>
@@ -14552,6 +15302,9 @@
       <c r="E250" t="s">
         <v>1370</v>
       </c>
+      <c r="F250" t="s">
+        <v>1454</v>
+      </c>
       <c r="G250" t="s">
         <v>990</v>
       </c>
@@ -14572,8 +15325,8 @@
       </c>
     </row>
     <row r="251" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A251">
-        <v>122</v>
+      <c r="A251" t="s">
+        <v>1455</v>
       </c>
       <c r="B251" t="s">
         <v>712</v>
@@ -14587,10 +15340,13 @@
       <c r="E251" t="s">
         <v>1373</v>
       </c>
+      <c r="F251" t="s">
+        <v>1454</v>
+      </c>
     </row>
     <row r="252" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A252">
-        <v>120</v>
+      <c r="A252" t="s">
+        <v>1455</v>
       </c>
       <c r="B252" t="s">
         <v>703</v>
@@ -14604,6 +15360,9 @@
       <c r="E252" t="s">
         <v>1376</v>
       </c>
+      <c r="F252" t="s">
+        <v>1454</v>
+      </c>
       <c r="G252" t="s">
         <v>990</v>
       </c>
@@ -14624,8 +15383,8 @@
       </c>
     </row>
     <row r="253" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A253">
-        <v>121</v>
+      <c r="A253" t="s">
+        <v>1455</v>
       </c>
       <c r="B253" t="s">
         <v>703</v>
@@ -14639,6 +15398,9 @@
       <c r="E253" t="s">
         <v>1379</v>
       </c>
+      <c r="F253" t="s">
+        <v>1454</v>
+      </c>
       <c r="G253" t="s">
         <v>997</v>
       </c>
@@ -14656,8 +15418,8 @@
       </c>
     </row>
     <row r="254" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A254">
-        <v>123</v>
+      <c r="A254" t="s">
+        <v>1455</v>
       </c>
       <c r="B254" t="s">
         <v>712</v>
@@ -14671,6 +15433,9 @@
       <c r="E254" t="s">
         <v>1381</v>
       </c>
+      <c r="F254" t="s">
+        <v>1454</v>
+      </c>
       <c r="G254" t="s">
         <v>980</v>
       </c>
@@ -14688,8 +15453,8 @@
       </c>
     </row>
     <row r="255" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A255">
-        <v>122</v>
+      <c r="A255" t="s">
+        <v>1455</v>
       </c>
       <c r="B255" t="s">
         <v>703</v>
@@ -14703,6 +15468,9 @@
       <c r="E255" t="s">
         <v>1384</v>
       </c>
+      <c r="F255" t="s">
+        <v>1454</v>
+      </c>
       <c r="G255" t="s">
         <v>990</v>
       </c>
@@ -14720,8 +15488,8 @@
       </c>
     </row>
     <row r="256" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A256">
-        <v>124</v>
+      <c r="A256" t="s">
+        <v>1455</v>
       </c>
       <c r="B256" t="s">
         <v>712</v>
@@ -14735,6 +15503,9 @@
       <c r="E256" t="s">
         <v>1387</v>
       </c>
+      <c r="F256" t="s">
+        <v>1454</v>
+      </c>
       <c r="G256" t="s">
         <v>716</v>
       </c>
@@ -14752,8 +15523,8 @@
       </c>
     </row>
     <row r="257" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A257">
-        <v>123</v>
+      <c r="A257" t="s">
+        <v>1455</v>
       </c>
       <c r="B257" t="s">
         <v>703</v>
@@ -14767,6 +15538,9 @@
       <c r="E257" t="s">
         <v>1390</v>
       </c>
+      <c r="F257" t="s">
+        <v>1454</v>
+      </c>
       <c r="G257" t="s">
         <v>997</v>
       </c>
@@ -14784,8 +15558,8 @@
       </c>
     </row>
     <row r="258" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A258">
-        <v>125</v>
+      <c r="A258" t="s">
+        <v>1455</v>
       </c>
       <c r="B258" t="s">
         <v>712</v>
@@ -14799,6 +15573,9 @@
       <c r="E258" t="s">
         <v>1393</v>
       </c>
+      <c r="F258" t="s">
+        <v>1454</v>
+      </c>
       <c r="G258" t="s">
         <v>980</v>
       </c>
@@ -14816,8 +15593,8 @@
       </c>
     </row>
     <row r="259" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A259">
-        <v>124</v>
+      <c r="A259" t="s">
+        <v>1455</v>
       </c>
       <c r="B259" t="s">
         <v>703</v>
@@ -14831,6 +15608,9 @@
       <c r="E259" t="s">
         <v>1396</v>
       </c>
+      <c r="F259" t="s">
+        <v>1454</v>
+      </c>
       <c r="G259" t="s">
         <v>997</v>
       </c>
@@ -14845,8 +15625,8 @@
       </c>
     </row>
     <row r="260" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A260">
-        <v>126</v>
+      <c r="A260" t="s">
+        <v>1455</v>
       </c>
       <c r="B260" t="s">
         <v>712</v>
@@ -14860,6 +15640,9 @@
       <c r="E260" t="s">
         <v>1399</v>
       </c>
+      <c r="F260" t="s">
+        <v>1454</v>
+      </c>
       <c r="G260" t="s">
         <v>716</v>
       </c>
@@ -14877,8 +15660,8 @@
       </c>
     </row>
     <row r="261" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A261">
-        <v>125</v>
+      <c r="A261" t="s">
+        <v>1455</v>
       </c>
       <c r="B261" t="s">
         <v>703</v>
@@ -14892,6 +15675,9 @@
       <c r="E261" t="s">
         <v>1402</v>
       </c>
+      <c r="F261" t="s">
+        <v>1454</v>
+      </c>
       <c r="G261" t="s">
         <v>990</v>
       </c>
@@ -14909,8 +15695,8 @@
       </c>
     </row>
     <row r="262" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A262">
-        <v>127</v>
+      <c r="A262" t="s">
+        <v>1455</v>
       </c>
       <c r="B262" t="s">
         <v>712</v>
@@ -14924,6 +15710,9 @@
       <c r="E262" t="s">
         <v>1405</v>
       </c>
+      <c r="F262" t="s">
+        <v>1454</v>
+      </c>
       <c r="G262" t="s">
         <v>716</v>
       </c>
@@ -14941,8 +15730,8 @@
       </c>
     </row>
     <row r="263" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A263">
-        <v>126</v>
+      <c r="A263" t="s">
+        <v>1455</v>
       </c>
       <c r="B263" t="s">
         <v>703</v>
@@ -14956,6 +15745,9 @@
       <c r="E263" t="s">
         <v>1408</v>
       </c>
+      <c r="F263" t="s">
+        <v>1454</v>
+      </c>
       <c r="G263" t="s">
         <v>997</v>
       </c>
@@ -14973,8 +15765,8 @@
       </c>
     </row>
     <row r="264" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A264">
-        <v>128</v>
+      <c r="A264" t="s">
+        <v>1455</v>
       </c>
       <c r="B264" t="s">
         <v>712</v>
@@ -14988,10 +15780,13 @@
       <c r="E264" t="s">
         <v>1411</v>
       </c>
+      <c r="F264" t="s">
+        <v>1454</v>
+      </c>
     </row>
     <row r="265" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A265">
-        <v>127</v>
+      <c r="A265" t="s">
+        <v>1455</v>
       </c>
       <c r="B265" t="s">
         <v>703</v>
@@ -15005,6 +15800,9 @@
       <c r="E265" t="s">
         <v>1414</v>
       </c>
+      <c r="F265" t="s">
+        <v>1454</v>
+      </c>
       <c r="G265" t="s">
         <v>990</v>
       </c>
@@ -15019,8 +15817,8 @@
       </c>
     </row>
     <row r="266" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A266">
-        <v>129</v>
+      <c r="A266" t="s">
+        <v>1455</v>
       </c>
       <c r="B266" t="s">
         <v>712</v>
@@ -15034,6 +15832,9 @@
       <c r="E266" t="s">
         <v>1417</v>
       </c>
+      <c r="F266" t="s">
+        <v>1454</v>
+      </c>
       <c r="G266" t="s">
         <v>980</v>
       </c>
@@ -15051,8 +15852,8 @@
       </c>
     </row>
     <row r="267" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A267">
-        <v>128</v>
+      <c r="A267" t="s">
+        <v>1455</v>
       </c>
       <c r="B267" t="s">
         <v>703</v>
@@ -15066,6 +15867,9 @@
       <c r="E267" t="s">
         <v>1420</v>
       </c>
+      <c r="F267" t="s">
+        <v>1454</v>
+      </c>
       <c r="G267" t="s">
         <v>997</v>
       </c>
@@ -15083,8 +15887,8 @@
       </c>
     </row>
     <row r="268" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A268">
-        <v>130</v>
+      <c r="A268" t="s">
+        <v>1455</v>
       </c>
       <c r="B268" t="s">
         <v>712</v>
@@ -15098,6 +15902,9 @@
       <c r="E268" t="s">
         <v>1423</v>
       </c>
+      <c r="F268" t="s">
+        <v>1454</v>
+      </c>
       <c r="G268" t="s">
         <v>716</v>
       </c>
@@ -15115,8 +15922,8 @@
       </c>
     </row>
     <row r="269" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A269">
-        <v>129</v>
+      <c r="A269" t="s">
+        <v>1455</v>
       </c>
       <c r="B269" t="s">
         <v>703</v>
@@ -15130,6 +15937,9 @@
       <c r="E269" t="s">
         <v>1425</v>
       </c>
+      <c r="F269" t="s">
+        <v>1454</v>
+      </c>
       <c r="G269" t="s">
         <v>990</v>
       </c>
@@ -15147,8 +15957,8 @@
       </c>
     </row>
     <row r="270" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A270">
-        <v>131</v>
+      <c r="A270" t="s">
+        <v>1455</v>
       </c>
       <c r="B270" t="s">
         <v>712</v>
@@ -15162,6 +15972,9 @@
       <c r="E270" t="s">
         <v>1427</v>
       </c>
+      <c r="F270" t="s">
+        <v>1454</v>
+      </c>
       <c r="G270" t="s">
         <v>980</v>
       </c>
@@ -15179,8 +15992,8 @@
       </c>
     </row>
     <row r="271" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A271">
-        <v>130</v>
+      <c r="A271" t="s">
+        <v>1455</v>
       </c>
       <c r="B271" t="s">
         <v>703</v>
@@ -15194,6 +16007,9 @@
       <c r="E271" t="s">
         <v>1430</v>
       </c>
+      <c r="F271" t="s">
+        <v>1454</v>
+      </c>
       <c r="G271" t="s">
         <v>990</v>
       </c>
@@ -15211,8 +16027,8 @@
       </c>
     </row>
     <row r="272" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A272">
-        <v>132</v>
+      <c r="A272" t="s">
+        <v>1455</v>
       </c>
       <c r="B272" t="s">
         <v>712</v>
@@ -15226,6 +16042,9 @@
       <c r="E272" t="s">
         <v>1432</v>
       </c>
+      <c r="F272" t="s">
+        <v>1454</v>
+      </c>
       <c r="G272" t="s">
         <v>734</v>
       </c>
@@ -15243,8 +16062,8 @@
       </c>
     </row>
     <row r="273" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A273">
-        <v>131</v>
+      <c r="A273" t="s">
+        <v>1455</v>
       </c>
       <c r="B273" t="s">
         <v>703</v>
@@ -15258,6 +16077,9 @@
       <c r="E273" t="s">
         <v>1435</v>
       </c>
+      <c r="F273" t="s">
+        <v>1454</v>
+      </c>
       <c r="G273" t="s">
         <v>997</v>
       </c>
@@ -15275,8 +16097,8 @@
       </c>
     </row>
     <row r="274" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A274">
-        <v>133</v>
+      <c r="A274" t="s">
+        <v>1455</v>
       </c>
       <c r="B274" t="s">
         <v>712</v>
@@ -15290,6 +16112,9 @@
       <c r="E274" t="s">
         <v>1438</v>
       </c>
+      <c r="F274" t="s">
+        <v>1454</v>
+      </c>
       <c r="G274" t="s">
         <v>716</v>
       </c>
@@ -15307,8 +16132,8 @@
       </c>
     </row>
     <row r="275" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A275">
-        <v>132</v>
+      <c r="A275" t="s">
+        <v>1455</v>
       </c>
       <c r="B275" t="s">
         <v>703</v>
@@ -15322,6 +16147,9 @@
       <c r="E275" t="s">
         <v>1441</v>
       </c>
+      <c r="F275" t="s">
+        <v>1454</v>
+      </c>
       <c r="G275" t="s">
         <v>997</v>
       </c>
@@ -15339,8 +16167,8 @@
       </c>
     </row>
     <row r="276" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A276">
-        <v>134</v>
+      <c r="A276" t="s">
+        <v>1455</v>
       </c>
       <c r="B276" t="s">
         <v>712</v>
@@ -15354,6 +16182,9 @@
       <c r="E276" t="s">
         <v>1442</v>
       </c>
+      <c r="F276" t="s">
+        <v>1454</v>
+      </c>
       <c r="G276" t="s">
         <v>980</v>
       </c>
@@ -15371,8 +16202,8 @@
       </c>
     </row>
     <row r="277" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A277">
-        <v>133</v>
+      <c r="A277" t="s">
+        <v>1455</v>
       </c>
       <c r="B277" t="s">
         <v>703</v>
@@ -15386,6 +16217,9 @@
       <c r="E277" t="s">
         <v>1445</v>
       </c>
+      <c r="F277" t="s">
+        <v>1454</v>
+      </c>
       <c r="G277" t="s">
         <v>723</v>
       </c>
@@ -15403,8 +16237,8 @@
       </c>
     </row>
     <row r="278" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A278">
-        <v>135</v>
+      <c r="A278" t="s">
+        <v>1455</v>
       </c>
       <c r="B278" t="s">
         <v>712</v>
@@ -15418,6 +16252,9 @@
       <c r="E278" t="s">
         <v>1447</v>
       </c>
+      <c r="F278" t="s">
+        <v>1454</v>
+      </c>
       <c r="G278" t="s">
         <v>734</v>
       </c>
@@ -15435,8 +16272,8 @@
       </c>
     </row>
     <row r="279" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A279">
-        <v>134</v>
+      <c r="A279" t="s">
+        <v>1455</v>
       </c>
       <c r="B279" t="s">
         <v>703</v>
@@ -15450,6 +16287,9 @@
       <c r="E279" t="s">
         <v>1450</v>
       </c>
+      <c r="F279" t="s">
+        <v>1454</v>
+      </c>
       <c r="G279" t="s">
         <v>997</v>
       </c>
@@ -15467,8 +16307,8 @@
       </c>
     </row>
     <row r="280" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A280">
-        <v>136</v>
+      <c r="A280" t="s">
+        <v>1455</v>
       </c>
       <c r="B280" t="s">
         <v>712</v>
@@ -15482,6 +16322,9 @@
       <c r="E280" t="s">
         <v>1452</v>
       </c>
+      <c r="F280" t="s">
+        <v>1454</v>
+      </c>
       <c r="G280" t="s">
         <v>980</v>
       </c>
@@ -15499,8 +16342,8 @@
       </c>
     </row>
     <row r="281" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A281">
-        <v>3</v>
+      <c r="A281" t="s">
+        <v>1455</v>
       </c>
       <c r="B281" t="s">
         <v>973</v>
@@ -15513,6 +16356,9 @@
       </c>
       <c r="E281" t="s">
         <v>1453</v>
+      </c>
+      <c r="F281" t="s">
+        <v>1454</v>
       </c>
     </row>
   </sheetData>
